--- a/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-05-30.xlsx
+++ b/Input_data/IST_US_trad_eco_cal_2025-01-01_to_2025-05-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2619"/>
+  <dimension ref="A1:G2499"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66761,12 +66761,12 @@
     <row r="2353">
       <c r="A2353" t="inlineStr">
         <is>
-          <t>2025-05-19 02:50:00+05:30</t>
+          <t>2025-05-19 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B2353" t="inlineStr">
         <is>
-          <t>Fed Williams Speech</t>
+          <t>Fed Bostic Speech</t>
         </is>
       </c>
       <c r="C2353" t="inlineStr"/>
@@ -66780,12 +66780,12 @@
     <row r="2354">
       <c r="A2354" t="inlineStr">
         <is>
-          <t>2025-05-19 18:00:00+05:30</t>
+          <t>2025-05-19 18:15:00+05:30</t>
         </is>
       </c>
       <c r="B2354" t="inlineStr">
         <is>
-          <t>Fed Bostic Speech</t>
+          <t>Fed Williams Speech</t>
         </is>
       </c>
       <c r="C2354" t="inlineStr"/>
@@ -66799,12 +66799,12 @@
     <row r="2355">
       <c r="A2355" t="inlineStr">
         <is>
-          <t>2025-05-19 18:00:00+05:30</t>
+          <t>2025-05-19 18:15:00+05:30</t>
         </is>
       </c>
       <c r="B2355" t="inlineStr">
         <is>
-          <t>Fed Bostic Speech</t>
+          <t>Fed Jefferson Speech</t>
         </is>
       </c>
       <c r="C2355" t="inlineStr"/>
@@ -66818,110 +66818,142 @@
     <row r="2356">
       <c r="A2356" t="inlineStr">
         <is>
-          <t>2025-05-19 18:15:00+05:30</t>
+          <t>2025-05-19 19:30:00+05:30</t>
         </is>
       </c>
       <c r="B2356" t="inlineStr">
         <is>
-          <t>Fed Jefferson Speech</t>
-        </is>
-      </c>
-      <c r="C2356" t="inlineStr"/>
-      <c r="D2356" t="inlineStr"/>
-      <c r="E2356" t="inlineStr"/>
-      <c r="F2356" t="inlineStr"/>
+          <t>CB Leading Index MoMAPR</t>
+        </is>
+      </c>
+      <c r="C2356" t="inlineStr">
+        <is>
+          <t>-1%</t>
+        </is>
+      </c>
+      <c r="D2356" t="inlineStr">
+        <is>
+          <t>-0.8%</t>
+        </is>
+      </c>
+      <c r="E2356" t="inlineStr">
+        <is>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="F2356" t="inlineStr">
+        <is>
+          <t>-0.6%</t>
+        </is>
+      </c>
       <c r="G2356" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2357">
       <c r="A2357" t="inlineStr">
         <is>
-          <t>2025-05-19 18:15:00+05:30</t>
+          <t>2025-05-19 19:30:00+05:30</t>
         </is>
       </c>
       <c r="B2357" t="inlineStr">
         <is>
-          <t>Fed Williams Speech</t>
+          <t>CB Leading Index MoMAPR</t>
         </is>
       </c>
       <c r="C2357" t="inlineStr"/>
-      <c r="D2357" t="inlineStr"/>
-      <c r="E2357" t="inlineStr"/>
-      <c r="F2357" t="inlineStr"/>
+      <c r="D2357" t="inlineStr">
+        <is>
+          <t>-0.7%</t>
+        </is>
+      </c>
+      <c r="E2357" t="inlineStr">
+        <is>
+          <t>-0.9%</t>
+        </is>
+      </c>
+      <c r="F2357" t="inlineStr">
+        <is>
+          <t>-0.6%</t>
+        </is>
+      </c>
       <c r="G2357" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2358">
       <c r="A2358" t="inlineStr">
         <is>
-          <t>2025-05-19 18:15:00+05:30</t>
+          <t>2025-05-19 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B2358" t="inlineStr">
         <is>
-          <t>Fed Williams Speech</t>
-        </is>
-      </c>
-      <c r="C2358" t="inlineStr"/>
-      <c r="D2358" t="inlineStr"/>
+          <t>6-Month Bill Auction</t>
+        </is>
+      </c>
+      <c r="C2358" t="inlineStr">
+        <is>
+          <t>4.140%</t>
+        </is>
+      </c>
+      <c r="D2358" t="inlineStr">
+        <is>
+          <t>4.105%</t>
+        </is>
+      </c>
       <c r="E2358" t="inlineStr"/>
       <c r="F2358" t="inlineStr"/>
       <c r="G2358" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2359">
       <c r="A2359" t="inlineStr">
         <is>
-          <t>2025-05-19 18:15:00+05:30</t>
+          <t>2025-05-19 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B2359" t="inlineStr">
         <is>
-          <t>Fed Jefferson Speech</t>
-        </is>
-      </c>
-      <c r="C2359" t="inlineStr"/>
-      <c r="D2359" t="inlineStr"/>
+          <t>3-Month Bill Auction</t>
+        </is>
+      </c>
+      <c r="C2359" t="inlineStr">
+        <is>
+          <t>4.285%</t>
+        </is>
+      </c>
+      <c r="D2359" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
       <c r="E2359" t="inlineStr"/>
       <c r="F2359" t="inlineStr"/>
       <c r="G2359" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2360">
       <c r="A2360" t="inlineStr">
         <is>
-          <t>2025-05-19 19:30:00+05:30</t>
+          <t>2025-05-19 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B2360" t="inlineStr">
         <is>
-          <t>CB Leading Index MoMAPR</t>
-        </is>
-      </c>
-      <c r="C2360" t="inlineStr">
-        <is>
-          <t>-1%</t>
-        </is>
-      </c>
+          <t>3-Month Bill Auction</t>
+        </is>
+      </c>
+      <c r="C2360" t="inlineStr"/>
       <c r="D2360" t="inlineStr">
         <is>
-          <t>-0.8%</t>
-        </is>
-      </c>
-      <c r="E2360" t="inlineStr">
-        <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="F2360" t="inlineStr">
-        <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="E2360" t="inlineStr"/>
+      <c r="F2360" t="inlineStr"/>
       <c r="G2360" t="n">
         <v>3</v>
       </c>
@@ -66929,30 +66961,22 @@
     <row r="2361">
       <c r="A2361" t="inlineStr">
         <is>
-          <t>2025-05-19 19:30:00+05:30</t>
+          <t>2025-05-19 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B2361" t="inlineStr">
         <is>
-          <t>CB Leading Index MoMAPR</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C2361" t="inlineStr"/>
       <c r="D2361" t="inlineStr">
         <is>
-          <t>-0.7%</t>
-        </is>
-      </c>
-      <c r="E2361" t="inlineStr">
-        <is>
-          <t>-0.9%</t>
-        </is>
-      </c>
-      <c r="F2361" t="inlineStr">
-        <is>
-          <t>-0.6%</t>
-        </is>
-      </c>
+          <t>4.105%</t>
+        </is>
+      </c>
+      <c r="E2361" t="inlineStr"/>
+      <c r="F2361" t="inlineStr"/>
       <c r="G2361" t="n">
         <v>3</v>
       </c>
@@ -66960,72 +66984,56 @@
     <row r="2362">
       <c r="A2362" t="inlineStr">
         <is>
-          <t>2025-05-19 21:00:00+05:30</t>
+          <t>2025-05-19 22:45:00+05:30</t>
         </is>
       </c>
       <c r="B2362" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
-        </is>
-      </c>
-      <c r="C2362" t="inlineStr">
-        <is>
-          <t>4.140%</t>
-        </is>
-      </c>
-      <c r="D2362" t="inlineStr">
-        <is>
-          <t>4.105%</t>
-        </is>
-      </c>
+          <t>Fed Logan Speech</t>
+        </is>
+      </c>
+      <c r="C2362" t="inlineStr"/>
+      <c r="D2362" t="inlineStr"/>
       <c r="E2362" t="inlineStr"/>
       <c r="F2362" t="inlineStr"/>
       <c r="G2362" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2363">
       <c r="A2363" t="inlineStr">
         <is>
-          <t>2025-05-19 21:00:00+05:30</t>
+          <t>2025-05-19 23:00:00+05:30</t>
         </is>
       </c>
       <c r="B2363" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
-        </is>
-      </c>
-      <c r="C2363" t="inlineStr">
-        <is>
-          <t>4.285%</t>
-        </is>
-      </c>
-      <c r="D2363" t="inlineStr">
-        <is>
-          <t>4.3%</t>
-        </is>
-      </c>
+          <t>Fed Kashkari Speech</t>
+        </is>
+      </c>
+      <c r="C2363" t="inlineStr"/>
+      <c r="D2363" t="inlineStr"/>
       <c r="E2363" t="inlineStr"/>
       <c r="F2363" t="inlineStr"/>
       <c r="G2363" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2364">
       <c r="A2364" t="inlineStr">
         <is>
-          <t>2025-05-19 21:00:00+05:30</t>
+          <t>2025-05-20 18:25:00+05:30</t>
         </is>
       </c>
       <c r="B2364" t="inlineStr">
         <is>
-          <t>3-Month Bill Auction</t>
+          <t>Redbook YoYMAY/17</t>
         </is>
       </c>
       <c r="C2364" t="inlineStr"/>
       <c r="D2364" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="E2364" t="inlineStr"/>
@@ -67037,35 +67045,31 @@
     <row r="2365">
       <c r="A2365" t="inlineStr">
         <is>
-          <t>2025-05-19 21:00:00+05:30</t>
+          <t>2025-05-20 18:30:00+05:30</t>
         </is>
       </c>
       <c r="B2365" t="inlineStr">
         <is>
-          <t>6-Month Bill Auction</t>
+          <t>Fed Barkin Speech</t>
         </is>
       </c>
       <c r="C2365" t="inlineStr"/>
-      <c r="D2365" t="inlineStr">
-        <is>
-          <t>4.105%</t>
-        </is>
-      </c>
+      <c r="D2365" t="inlineStr"/>
       <c r="E2365" t="inlineStr"/>
       <c r="F2365" t="inlineStr"/>
       <c r="G2365" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2366">
       <c r="A2366" t="inlineStr">
         <is>
-          <t>2025-05-19 22:45:00+05:30</t>
+          <t>2025-05-20 18:30:00+05:30</t>
         </is>
       </c>
       <c r="B2366" t="inlineStr">
         <is>
-          <t>Fed Logan Speech</t>
+          <t>Fed Bostic Speech</t>
         </is>
       </c>
       <c r="C2366" t="inlineStr"/>
@@ -67079,12 +67083,12 @@
     <row r="2367">
       <c r="A2367" t="inlineStr">
         <is>
-          <t>2025-05-19 22:45:00+05:30</t>
+          <t>2025-05-20 19:00:00+05:30</t>
         </is>
       </c>
       <c r="B2367" t="inlineStr">
         <is>
-          <t>Fed Logan Speech</t>
+          <t>Fed Collins Speech</t>
         </is>
       </c>
       <c r="C2367" t="inlineStr"/>
@@ -67098,12 +67102,12 @@
     <row r="2368">
       <c r="A2368" t="inlineStr">
         <is>
-          <t>2025-05-19 23:00:00+05:30</t>
+          <t>2025-05-20 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B2368" t="inlineStr">
         <is>
-          <t>Fed Kashkari Speech</t>
+          <t>Fed Musalem Speech</t>
         </is>
       </c>
       <c r="C2368" t="inlineStr"/>
@@ -67117,16 +67121,20 @@
     <row r="2369">
       <c r="A2369" t="inlineStr">
         <is>
-          <t>2025-05-19 23:00:00+05:30</t>
+          <t>2025-05-21 02:00:00+05:30</t>
         </is>
       </c>
       <c r="B2369" t="inlineStr">
         <is>
-          <t>Fed Kashkari Speech</t>
+          <t>API Crude Oil Stock ChangeMAY/16</t>
         </is>
       </c>
       <c r="C2369" t="inlineStr"/>
-      <c r="D2369" t="inlineStr"/>
+      <c r="D2369" t="inlineStr">
+        <is>
+          <t>4.287M</t>
+        </is>
+      </c>
       <c r="E2369" t="inlineStr"/>
       <c r="F2369" t="inlineStr"/>
       <c r="G2369" t="n">
@@ -67136,58 +67144,50 @@
     <row r="2370">
       <c r="A2370" t="inlineStr">
         <is>
-          <t>2025-05-20 18:25:00+05:30</t>
+          <t>2025-05-21 02:30:00+05:30</t>
         </is>
       </c>
       <c r="B2370" t="inlineStr">
         <is>
-          <t>Redbook YoYMAY/17</t>
+          <t>Fed Kugler Speech</t>
         </is>
       </c>
       <c r="C2370" t="inlineStr"/>
-      <c r="D2370" t="inlineStr">
-        <is>
-          <t>5.8%</t>
-        </is>
-      </c>
+      <c r="D2370" t="inlineStr"/>
       <c r="E2370" t="inlineStr"/>
       <c r="F2370" t="inlineStr"/>
       <c r="G2370" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2371">
       <c r="A2371" t="inlineStr">
         <is>
-          <t>2025-05-20 18:25:00+05:30</t>
+          <t>2025-05-21 04:30:00+05:30</t>
         </is>
       </c>
       <c r="B2371" t="inlineStr">
         <is>
-          <t>Redbook YoYMAY/17</t>
+          <t>Fed Daly Speech</t>
         </is>
       </c>
       <c r="C2371" t="inlineStr"/>
-      <c r="D2371" t="inlineStr">
-        <is>
-          <t>5.8%</t>
-        </is>
-      </c>
+      <c r="D2371" t="inlineStr"/>
       <c r="E2371" t="inlineStr"/>
       <c r="F2371" t="inlineStr"/>
       <c r="G2371" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2372">
       <c r="A2372" t="inlineStr">
         <is>
-          <t>2025-05-20 18:30:00+05:30</t>
+          <t>2025-05-21 04:30:00+05:30</t>
         </is>
       </c>
       <c r="B2372" t="inlineStr">
         <is>
-          <t>Fed Bostic Speech</t>
+          <t>Fed Hammack Speech</t>
         </is>
       </c>
       <c r="C2372" t="inlineStr"/>
@@ -67201,73 +67201,89 @@
     <row r="2373">
       <c r="A2373" t="inlineStr">
         <is>
-          <t>2025-05-20 18:30:00+05:30</t>
+          <t>2025-05-21 16:30:00+05:30</t>
         </is>
       </c>
       <c r="B2373" t="inlineStr">
         <is>
-          <t>Fed Barkin Speech</t>
+          <t>MBA Mortgage Market IndexMAY/16</t>
         </is>
       </c>
       <c r="C2373" t="inlineStr"/>
-      <c r="D2373" t="inlineStr"/>
+      <c r="D2373" t="inlineStr">
+        <is>
+          <t>251.2</t>
+        </is>
+      </c>
       <c r="E2373" t="inlineStr"/>
       <c r="F2373" t="inlineStr"/>
       <c r="G2373" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2374">
       <c r="A2374" t="inlineStr">
         <is>
-          <t>2025-05-20 18:30:00+05:30</t>
+          <t>2025-05-21 16:30:00+05:30</t>
         </is>
       </c>
       <c r="B2374" t="inlineStr">
         <is>
-          <t>Fed Barkin Speech</t>
+          <t>MBA Purchase IndexMAY/16</t>
         </is>
       </c>
       <c r="C2374" t="inlineStr"/>
-      <c r="D2374" t="inlineStr"/>
+      <c r="D2374" t="inlineStr">
+        <is>
+          <t>166.5</t>
+        </is>
+      </c>
       <c r="E2374" t="inlineStr"/>
       <c r="F2374" t="inlineStr"/>
       <c r="G2374" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2375">
       <c r="A2375" t="inlineStr">
         <is>
-          <t>2025-05-20 18:30:00+05:30</t>
+          <t>2025-05-21 16:30:00+05:30</t>
         </is>
       </c>
       <c r="B2375" t="inlineStr">
         <is>
-          <t>Fed Bostic Speech</t>
+          <t>MBA Mortgage Refinance IndexMAY/16</t>
         </is>
       </c>
       <c r="C2375" t="inlineStr"/>
-      <c r="D2375" t="inlineStr"/>
+      <c r="D2375" t="inlineStr">
+        <is>
+          <t>718.1</t>
+        </is>
+      </c>
       <c r="E2375" t="inlineStr"/>
       <c r="F2375" t="inlineStr"/>
       <c r="G2375" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2376">
       <c r="A2376" t="inlineStr">
         <is>
-          <t>2025-05-20 19:00:00+05:30</t>
+          <t>2025-05-21 16:30:00+05:30</t>
         </is>
       </c>
       <c r="B2376" t="inlineStr">
         <is>
-          <t>Fed Collins Speech</t>
+          <t>MBA 30-Year Mortgage RateMAY/16</t>
         </is>
       </c>
       <c r="C2376" t="inlineStr"/>
-      <c r="D2376" t="inlineStr"/>
+      <c r="D2376" t="inlineStr">
+        <is>
+          <t>6.86%</t>
+        </is>
+      </c>
       <c r="E2376" t="inlineStr"/>
       <c r="F2376" t="inlineStr"/>
       <c r="G2376" t="n">
@@ -67277,54 +67293,66 @@
     <row r="2377">
       <c r="A2377" t="inlineStr">
         <is>
-          <t>2025-05-20 19:00:00+05:30</t>
+          <t>2025-05-21 16:30:00+05:30</t>
         </is>
       </c>
       <c r="B2377" t="inlineStr">
         <is>
-          <t>Fed Collins Speech</t>
+          <t>MBA Mortgage ApplicationsMAY/16</t>
         </is>
       </c>
       <c r="C2377" t="inlineStr"/>
-      <c r="D2377" t="inlineStr"/>
+      <c r="D2377" t="inlineStr">
+        <is>
+          <t>1.1%</t>
+        </is>
+      </c>
       <c r="E2377" t="inlineStr"/>
       <c r="F2377" t="inlineStr"/>
       <c r="G2377" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2378">
       <c r="A2378" t="inlineStr">
         <is>
-          <t>2025-05-20 22:30:00+05:30</t>
+          <t>2025-05-21 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B2378" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Crude Oil Imports ChangeMAY/16</t>
         </is>
       </c>
       <c r="C2378" t="inlineStr"/>
-      <c r="D2378" t="inlineStr"/>
+      <c r="D2378" t="inlineStr">
+        <is>
+          <t>0.422M</t>
+        </is>
+      </c>
       <c r="E2378" t="inlineStr"/>
       <c r="F2378" t="inlineStr"/>
       <c r="G2378" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2379">
       <c r="A2379" t="inlineStr">
         <is>
-          <t>2025-05-20 22:30:00+05:30</t>
+          <t>2025-05-21 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B2379" t="inlineStr">
         <is>
-          <t>Fed Musalem Speech</t>
+          <t>EIA Gasoline Stocks ChangeMAY/16</t>
         </is>
       </c>
       <c r="C2379" t="inlineStr"/>
-      <c r="D2379" t="inlineStr"/>
+      <c r="D2379" t="inlineStr">
+        <is>
+          <t>-1.022M</t>
+        </is>
+      </c>
       <c r="E2379" t="inlineStr"/>
       <c r="F2379" t="inlineStr"/>
       <c r="G2379" t="n">
@@ -67334,138 +67362,158 @@
     <row r="2380">
       <c r="A2380" t="inlineStr">
         <is>
-          <t>2025-05-21 02:00:00+05:30</t>
+          <t>2025-05-21 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B2380" t="inlineStr">
         <is>
-          <t>API Crude Oil Stock ChangeMAY/16</t>
+          <t>EIA Gasoline Production ChangeMAY/16</t>
         </is>
       </c>
       <c r="C2380" t="inlineStr"/>
       <c r="D2380" t="inlineStr">
         <is>
-          <t>4.287M</t>
+          <t>-0.327M</t>
         </is>
       </c>
       <c r="E2380" t="inlineStr"/>
       <c r="F2380" t="inlineStr"/>
       <c r="G2380" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2381">
       <c r="A2381" t="inlineStr">
         <is>
-          <t>2025-05-21 02:00:00+05:30</t>
+          <t>2025-05-21 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B2381" t="inlineStr">
         <is>
-          <t>API Crude Oil Stock ChangeMAY/16</t>
+          <t>EIA Heating Oil Stocks ChangeMAY/16</t>
         </is>
       </c>
       <c r="C2381" t="inlineStr"/>
       <c r="D2381" t="inlineStr">
         <is>
-          <t>4.287M</t>
+          <t>0.292M</t>
         </is>
       </c>
       <c r="E2381" t="inlineStr"/>
       <c r="F2381" t="inlineStr"/>
       <c r="G2381" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2382">
       <c r="A2382" t="inlineStr">
         <is>
-          <t>2025-05-21 02:30:00+05:30</t>
+          <t>2025-05-21 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B2382" t="inlineStr">
         <is>
-          <t>Fed Kugler Speech</t>
+          <t>EIA Refinery Crude Runs ChangeMAY/16</t>
         </is>
       </c>
       <c r="C2382" t="inlineStr"/>
-      <c r="D2382" t="inlineStr"/>
+      <c r="D2382" t="inlineStr">
+        <is>
+          <t>0.33M</t>
+        </is>
+      </c>
       <c r="E2382" t="inlineStr"/>
       <c r="F2382" t="inlineStr"/>
       <c r="G2382" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2383">
       <c r="A2383" t="inlineStr">
         <is>
-          <t>2025-05-21 02:30:00+05:30</t>
+          <t>2025-05-21 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B2383" t="inlineStr">
         <is>
-          <t>Fed Kugler Speech</t>
+          <t>EIA Distillate Stocks ChangeMAY/16</t>
         </is>
       </c>
       <c r="C2383" t="inlineStr"/>
-      <c r="D2383" t="inlineStr"/>
+      <c r="D2383" t="inlineStr">
+        <is>
+          <t>-3.155M</t>
+        </is>
+      </c>
       <c r="E2383" t="inlineStr"/>
       <c r="F2383" t="inlineStr"/>
       <c r="G2383" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2384">
       <c r="A2384" t="inlineStr">
         <is>
-          <t>2025-05-21 04:30:00+05:30</t>
+          <t>2025-05-21 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B2384" t="inlineStr">
         <is>
-          <t>Fed Hammack Speech</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeMAY/16</t>
         </is>
       </c>
       <c r="C2384" t="inlineStr"/>
-      <c r="D2384" t="inlineStr"/>
+      <c r="D2384" t="inlineStr">
+        <is>
+          <t>-1.069M</t>
+        </is>
+      </c>
       <c r="E2384" t="inlineStr"/>
       <c r="F2384" t="inlineStr"/>
       <c r="G2384" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2385">
       <c r="A2385" t="inlineStr">
         <is>
-          <t>2025-05-21 04:30:00+05:30</t>
+          <t>2025-05-21 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B2385" t="inlineStr">
         <is>
-          <t>Fed Daly Speech</t>
+          <t>EIA Distillate Fuel Production ChangeMAY/16</t>
         </is>
       </c>
       <c r="C2385" t="inlineStr"/>
-      <c r="D2385" t="inlineStr"/>
+      <c r="D2385" t="inlineStr">
+        <is>
+          <t>-0.069M</t>
+        </is>
+      </c>
       <c r="E2385" t="inlineStr"/>
       <c r="F2385" t="inlineStr"/>
       <c r="G2385" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2386">
       <c r="A2386" t="inlineStr">
         <is>
-          <t>2025-05-21 04:30:00+05:30</t>
+          <t>2025-05-21 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B2386" t="inlineStr">
         <is>
-          <t>Fed Daly Speech</t>
+          <t>EIA Crude Oil Stocks ChangeMAY/16</t>
         </is>
       </c>
       <c r="C2386" t="inlineStr"/>
-      <c r="D2386" t="inlineStr"/>
+      <c r="D2386" t="inlineStr">
+        <is>
+          <t>3.454M</t>
+        </is>
+      </c>
       <c r="E2386" t="inlineStr"/>
       <c r="F2386" t="inlineStr"/>
       <c r="G2386" t="n">
@@ -67475,60 +67523,60 @@
     <row r="2387">
       <c r="A2387" t="inlineStr">
         <is>
-          <t>2025-05-21 04:30:00+05:30</t>
+          <t>2025-05-21 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B2387" t="inlineStr">
         <is>
-          <t>Fed Hammack Speech</t>
+          <t>17-Week Bill Auction</t>
         </is>
       </c>
       <c r="C2387" t="inlineStr"/>
-      <c r="D2387" t="inlineStr"/>
+      <c r="D2387" t="inlineStr">
+        <is>
+          <t>4.240%</t>
+        </is>
+      </c>
       <c r="E2387" t="inlineStr"/>
       <c r="F2387" t="inlineStr"/>
       <c r="G2387" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2388">
       <c r="A2388" t="inlineStr">
         <is>
-          <t>2025-05-21 16:30:00+05:30</t>
+          <t>2025-05-21 21:30:00+05:30</t>
         </is>
       </c>
       <c r="B2388" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexMAY/16</t>
+          <t>Fed Barkin Speech</t>
         </is>
       </c>
       <c r="C2388" t="inlineStr"/>
-      <c r="D2388" t="inlineStr">
-        <is>
-          <t>251.2</t>
-        </is>
-      </c>
+      <c r="D2388" t="inlineStr"/>
       <c r="E2388" t="inlineStr"/>
       <c r="F2388" t="inlineStr"/>
       <c r="G2388" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2389">
       <c r="A2389" t="inlineStr">
         <is>
-          <t>2025-05-21 16:30:00+05:30</t>
+          <t>2025-05-21 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B2389" t="inlineStr">
         <is>
-          <t>MBA Mortgage Market IndexMAY/16</t>
+          <t>20-Year Bond Auction</t>
         </is>
       </c>
       <c r="C2389" t="inlineStr"/>
       <c r="D2389" t="inlineStr">
         <is>
-          <t>251.2</t>
+          <t>4.810%</t>
         </is>
       </c>
       <c r="E2389" t="inlineStr"/>
@@ -67540,45 +67588,53 @@
     <row r="2390">
       <c r="A2390" t="inlineStr">
         <is>
-          <t>2025-05-21 16:30:00+05:30</t>
+          <t>2025-05-22 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B2390" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsMAY/16</t>
+          <t>Chicago Fed National Activity IndexAPR</t>
         </is>
       </c>
       <c r="C2390" t="inlineStr"/>
       <c r="D2390" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="E2390" t="inlineStr"/>
-      <c r="F2390" t="inlineStr"/>
+      <c r="F2390" t="inlineStr">
+        <is>
+          <t>-0.2</t>
+        </is>
+      </c>
       <c r="G2390" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2391">
       <c r="A2391" t="inlineStr">
         <is>
-          <t>2025-05-21 16:30:00+05:30</t>
+          <t>2025-05-22 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B2391" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexMAY/16</t>
+          <t>Jobless Claims 4-week AverageMAY/17</t>
         </is>
       </c>
       <c r="C2391" t="inlineStr"/>
       <c r="D2391" t="inlineStr">
         <is>
-          <t>166.5</t>
+          <t>230.5K</t>
         </is>
       </c>
       <c r="E2391" t="inlineStr"/>
-      <c r="F2391" t="inlineStr"/>
+      <c r="F2391" t="inlineStr">
+        <is>
+          <t>231.0K</t>
+        </is>
+      </c>
       <c r="G2391" t="n">
         <v>3</v>
       </c>
@@ -67586,114 +67642,146 @@
     <row r="2392">
       <c r="A2392" t="inlineStr">
         <is>
-          <t>2025-05-21 16:30:00+05:30</t>
+          <t>2025-05-22 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B2392" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateMAY/16</t>
+          <t>Continuing Jobless ClaimsMAY/10</t>
         </is>
       </c>
       <c r="C2392" t="inlineStr"/>
       <c r="D2392" t="inlineStr">
         <is>
-          <t>6.86%</t>
+          <t>1881K</t>
         </is>
       </c>
       <c r="E2392" t="inlineStr"/>
-      <c r="F2392" t="inlineStr"/>
+      <c r="F2392" t="inlineStr">
+        <is>
+          <t>1885.0K</t>
+        </is>
+      </c>
       <c r="G2392" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2393">
       <c r="A2393" t="inlineStr">
         <is>
-          <t>2025-05-21 16:30:00+05:30</t>
+          <t>2025-05-22 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B2393" t="inlineStr">
         <is>
-          <t>MBA Purchase IndexMAY/16</t>
+          <t>Initial Jobless ClaimsMAY/17</t>
         </is>
       </c>
       <c r="C2393" t="inlineStr"/>
       <c r="D2393" t="inlineStr">
         <is>
-          <t>166.5</t>
-        </is>
-      </c>
-      <c r="E2393" t="inlineStr"/>
-      <c r="F2393" t="inlineStr"/>
+          <t>229K</t>
+        </is>
+      </c>
+      <c r="E2393" t="inlineStr">
+        <is>
+          <t>232K</t>
+        </is>
+      </c>
+      <c r="F2393" t="inlineStr">
+        <is>
+          <t>231.0K</t>
+        </is>
+      </c>
       <c r="G2393" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2394">
       <c r="A2394" t="inlineStr">
         <is>
-          <t>2025-05-21 16:30:00+05:30</t>
+          <t>2025-05-22 19:15:00+05:30</t>
         </is>
       </c>
       <c r="B2394" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexMAY/16</t>
+          <t>S&amp;P Global Composite PMI FlashMAY</t>
         </is>
       </c>
       <c r="C2394" t="inlineStr"/>
       <c r="D2394" t="inlineStr">
         <is>
-          <t>718.1</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="E2394" t="inlineStr"/>
-      <c r="F2394" t="inlineStr"/>
+      <c r="F2394" t="inlineStr">
+        <is>
+          <t>50.4</t>
+        </is>
+      </c>
       <c r="G2394" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2395">
       <c r="A2395" t="inlineStr">
         <is>
-          <t>2025-05-21 16:30:00+05:30</t>
+          <t>2025-05-22 19:15:00+05:30</t>
         </is>
       </c>
       <c r="B2395" t="inlineStr">
         <is>
-          <t>MBA Mortgage Refinance IndexMAY/16</t>
+          <t>S&amp;P Global Manufacturing PMI FlashMAY</t>
         </is>
       </c>
       <c r="C2395" t="inlineStr"/>
       <c r="D2395" t="inlineStr">
         <is>
-          <t>718.1</t>
-        </is>
-      </c>
-      <c r="E2395" t="inlineStr"/>
-      <c r="F2395" t="inlineStr"/>
+          <t>50.2</t>
+        </is>
+      </c>
+      <c r="E2395" t="inlineStr">
+        <is>
+          <t>50.5</t>
+        </is>
+      </c>
+      <c r="F2395" t="inlineStr">
+        <is>
+          <t>50.3</t>
+        </is>
+      </c>
       <c r="G2395" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2396">
       <c r="A2396" t="inlineStr">
         <is>
-          <t>2025-05-21 16:30:00+05:30</t>
+          <t>2025-05-22 19:15:00+05:30</t>
         </is>
       </c>
       <c r="B2396" t="inlineStr">
         <is>
-          <t>MBA 30-Year Mortgage RateMAY/16</t>
+          <t>S&amp;P Global Services PMI FlashMAY</t>
         </is>
       </c>
       <c r="C2396" t="inlineStr"/>
       <c r="D2396" t="inlineStr">
         <is>
-          <t>6.86%</t>
-        </is>
-      </c>
-      <c r="E2396" t="inlineStr"/>
-      <c r="F2396" t="inlineStr"/>
+          <t>50.8</t>
+        </is>
+      </c>
+      <c r="E2396" t="inlineStr">
+        <is>
+          <t>51.5</t>
+        </is>
+      </c>
+      <c r="F2396" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
       <c r="G2396" t="n">
         <v>2</v>
       </c>
@@ -67701,64 +67789,76 @@
     <row r="2397">
       <c r="A2397" t="inlineStr">
         <is>
-          <t>2025-05-21 16:30:00+05:30</t>
+          <t>2025-05-22 19:30:00+05:30</t>
         </is>
       </c>
       <c r="B2397" t="inlineStr">
         <is>
-          <t>MBA Mortgage ApplicationsMAY/16</t>
+          <t>Existing Home SalesAPR</t>
         </is>
       </c>
       <c r="C2397" t="inlineStr"/>
       <c r="D2397" t="inlineStr">
         <is>
-          <t>1.1%</t>
-        </is>
-      </c>
-      <c r="E2397" t="inlineStr"/>
-      <c r="F2397" t="inlineStr"/>
+          <t>4.02M</t>
+        </is>
+      </c>
+      <c r="E2397" t="inlineStr">
+        <is>
+          <t>4.1M</t>
+        </is>
+      </c>
+      <c r="F2397" t="inlineStr">
+        <is>
+          <t>3.9M</t>
+        </is>
+      </c>
       <c r="G2397" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2398">
       <c r="A2398" t="inlineStr">
         <is>
-          <t>2025-05-21 20:00:00+05:30</t>
+          <t>2025-05-22 19:30:00+05:30</t>
         </is>
       </c>
       <c r="B2398" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeMAY/16</t>
+          <t>Existing Home Sales MoMAPR</t>
         </is>
       </c>
       <c r="C2398" t="inlineStr"/>
       <c r="D2398" t="inlineStr">
         <is>
-          <t>0.422M</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="E2398" t="inlineStr"/>
-      <c r="F2398" t="inlineStr"/>
+      <c r="F2398" t="inlineStr">
+        <is>
+          <t>-3%</t>
+        </is>
+      </c>
       <c r="G2398" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2399">
       <c r="A2399" t="inlineStr">
         <is>
-          <t>2025-05-21 20:00:00+05:30</t>
+          <t>2025-05-22 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B2399" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Imports ChangeMAY/16</t>
+          <t>EIA Natural Gas Stocks ChangeMAY/16</t>
         </is>
       </c>
       <c r="C2399" t="inlineStr"/>
       <c r="D2399" t="inlineStr">
         <is>
-          <t>0.422M</t>
+          <t>110Bcf</t>
         </is>
       </c>
       <c r="E2399" t="inlineStr"/>
@@ -67770,45 +67870,53 @@
     <row r="2400">
       <c r="A2400" t="inlineStr">
         <is>
-          <t>2025-05-21 20:00:00+05:30</t>
+          <t>2025-05-22 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B2400" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeMAY/16</t>
+          <t>Kansas Fed Composite IndexMAY</t>
         </is>
       </c>
       <c r="C2400" t="inlineStr"/>
       <c r="D2400" t="inlineStr">
         <is>
-          <t>-1.022M</t>
+          <t>-4</t>
         </is>
       </c>
       <c r="E2400" t="inlineStr"/>
-      <c r="F2400" t="inlineStr"/>
+      <c r="F2400" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
       <c r="G2400" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2401">
       <c r="A2401" t="inlineStr">
         <is>
-          <t>2025-05-21 20:00:00+05:30</t>
+          <t>2025-05-22 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B2401" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeMAY/16</t>
+          <t>Kansas Fed Manufacturing IndexMAY</t>
         </is>
       </c>
       <c r="C2401" t="inlineStr"/>
       <c r="D2401" t="inlineStr">
         <is>
-          <t>0.33M</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="E2401" t="inlineStr"/>
-      <c r="F2401" t="inlineStr"/>
+      <c r="F2401" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
       <c r="G2401" t="n">
         <v>3</v>
       </c>
@@ -67816,18 +67924,18 @@
     <row r="2402">
       <c r="A2402" t="inlineStr">
         <is>
-          <t>2025-05-21 20:00:00+05:30</t>
+          <t>2025-05-22 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B2402" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeMAY/16</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C2402" t="inlineStr"/>
       <c r="D2402" t="inlineStr">
         <is>
-          <t>0.292M</t>
+          <t>4.22%</t>
         </is>
       </c>
       <c r="E2402" t="inlineStr"/>
@@ -67839,18 +67947,18 @@
     <row r="2403">
       <c r="A2403" t="inlineStr">
         <is>
-          <t>2025-05-21 20:00:00+05:30</t>
+          <t>2025-05-22 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B2403" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeMAY/16</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C2403" t="inlineStr"/>
       <c r="D2403" t="inlineStr">
         <is>
-          <t>-0.327M</t>
+          <t>4.235%</t>
         </is>
       </c>
       <c r="E2403" t="inlineStr"/>
@@ -67862,41 +67970,41 @@
     <row r="2404">
       <c r="A2404" t="inlineStr">
         <is>
-          <t>2025-05-21 20:00:00+05:30</t>
+          <t>2025-05-22 21:30:00+05:30</t>
         </is>
       </c>
       <c r="B2404" t="inlineStr">
         <is>
-          <t>EIA Gasoline Stocks ChangeMAY/16</t>
+          <t>10-Year TIPS Auction</t>
         </is>
       </c>
       <c r="C2404" t="inlineStr"/>
       <c r="D2404" t="inlineStr">
         <is>
-          <t>-1.022M</t>
+          <t>1.935%</t>
         </is>
       </c>
       <c r="E2404" t="inlineStr"/>
       <c r="F2404" t="inlineStr"/>
       <c r="G2404" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2405">
       <c r="A2405" t="inlineStr">
         <is>
-          <t>2025-05-21 20:00:00+05:30</t>
+          <t>2025-05-22 21:30:00+05:30</t>
         </is>
       </c>
       <c r="B2405" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeMAY/16</t>
+          <t>30-Year Mortgage RateMAY/22</t>
         </is>
       </c>
       <c r="C2405" t="inlineStr"/>
       <c r="D2405" t="inlineStr">
         <is>
-          <t>-0.069M</t>
+          <t>6.81%</t>
         </is>
       </c>
       <c r="E2405" t="inlineStr"/>
@@ -67908,18 +68016,18 @@
     <row r="2406">
       <c r="A2406" t="inlineStr">
         <is>
-          <t>2025-05-21 20:00:00+05:30</t>
+          <t>2025-05-22 21:30:00+05:30</t>
         </is>
       </c>
       <c r="B2406" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeMAY/16</t>
+          <t>15-Year Mortgage RateMAY/22</t>
         </is>
       </c>
       <c r="C2406" t="inlineStr"/>
       <c r="D2406" t="inlineStr">
         <is>
-          <t>-1.069M</t>
+          <t>5.92%</t>
         </is>
       </c>
       <c r="E2406" t="inlineStr"/>
@@ -67931,18 +68039,18 @@
     <row r="2407">
       <c r="A2407" t="inlineStr">
         <is>
-          <t>2025-05-21 20:00:00+05:30</t>
+          <t>2025-05-22 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B2407" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeMAY/16</t>
+          <t>10-Year TIPS Auction</t>
         </is>
       </c>
       <c r="C2407" t="inlineStr"/>
       <c r="D2407" t="inlineStr">
         <is>
-          <t>-3.155M</t>
+          <t>1.935%</t>
         </is>
       </c>
       <c r="E2407" t="inlineStr"/>
@@ -67954,41 +68062,37 @@
     <row r="2408">
       <c r="A2408" t="inlineStr">
         <is>
-          <t>2025-05-21 20:00:00+05:30</t>
+          <t>2025-05-22 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B2408" t="inlineStr">
         <is>
-          <t>EIA Gasoline Production ChangeMAY/16</t>
+          <t>Fed Williams Speech</t>
         </is>
       </c>
       <c r="C2408" t="inlineStr"/>
-      <c r="D2408" t="inlineStr">
-        <is>
-          <t>-0.327M</t>
-        </is>
-      </c>
+      <c r="D2408" t="inlineStr"/>
       <c r="E2408" t="inlineStr"/>
       <c r="F2408" t="inlineStr"/>
       <c r="G2408" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2409">
       <c r="A2409" t="inlineStr">
         <is>
-          <t>2025-05-21 20:00:00+05:30</t>
+          <t>2025-05-23 02:00:00+05:30</t>
         </is>
       </c>
       <c r="B2409" t="inlineStr">
         <is>
-          <t>EIA Heating Oil Stocks ChangeMAY/16</t>
+          <t>Building Permits FinalAPR</t>
         </is>
       </c>
       <c r="C2409" t="inlineStr"/>
       <c r="D2409" t="inlineStr">
         <is>
-          <t>0.292M</t>
+          <t>1.467M</t>
         </is>
       </c>
       <c r="E2409" t="inlineStr"/>
@@ -68000,18 +68104,18 @@
     <row r="2410">
       <c r="A2410" t="inlineStr">
         <is>
-          <t>2025-05-21 20:00:00+05:30</t>
+          <t>2025-05-23 02:00:00+05:30</t>
         </is>
       </c>
       <c r="B2410" t="inlineStr">
         <is>
-          <t>EIA Refinery Crude Runs ChangeMAY/16</t>
+          <t>Building Permits MoM FinalAPR</t>
         </is>
       </c>
       <c r="C2410" t="inlineStr"/>
       <c r="D2410" t="inlineStr">
         <is>
-          <t>0.33M</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E2410" t="inlineStr"/>
@@ -68023,18 +68127,18 @@
     <row r="2411">
       <c r="A2411" t="inlineStr">
         <is>
-          <t>2025-05-21 20:00:00+05:30</t>
+          <t>2025-05-23 02:00:00+05:30</t>
         </is>
       </c>
       <c r="B2411" t="inlineStr">
         <is>
-          <t>EIA Distillate Stocks ChangeMAY/16</t>
+          <t>Fed Balance SheetMAY/21</t>
         </is>
       </c>
       <c r="C2411" t="inlineStr"/>
       <c r="D2411" t="inlineStr">
         <is>
-          <t>-3.155M</t>
+          <t>$6.71T</t>
         </is>
       </c>
       <c r="E2411" t="inlineStr"/>
@@ -68046,18 +68150,18 @@
     <row r="2412">
       <c r="A2412" t="inlineStr">
         <is>
-          <t>2025-05-21 20:00:00+05:30</t>
+          <t>2025-05-23 19:30:00+05:30</t>
         </is>
       </c>
       <c r="B2412" t="inlineStr">
         <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeMAY/16</t>
+          <t>Building Permits FinalAPR</t>
         </is>
       </c>
       <c r="C2412" t="inlineStr"/>
       <c r="D2412" t="inlineStr">
         <is>
-          <t>-1.069M</t>
+          <t>1.467M</t>
         </is>
       </c>
       <c r="E2412" t="inlineStr"/>
@@ -68069,18 +68173,18 @@
     <row r="2413">
       <c r="A2413" t="inlineStr">
         <is>
-          <t>2025-05-21 20:00:00+05:30</t>
+          <t>2025-05-23 19:30:00+05:30</t>
         </is>
       </c>
       <c r="B2413" t="inlineStr">
         <is>
-          <t>EIA Distillate Fuel Production ChangeMAY/16</t>
+          <t>Building Permits MoM FinalAPR</t>
         </is>
       </c>
       <c r="C2413" t="inlineStr"/>
       <c r="D2413" t="inlineStr">
         <is>
-          <t>-0.069M</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E2413" t="inlineStr"/>
@@ -68092,22 +68196,30 @@
     <row r="2414">
       <c r="A2414" t="inlineStr">
         <is>
-          <t>2025-05-21 20:00:00+05:30</t>
+          <t>2025-05-23 19:30:00+05:30</t>
         </is>
       </c>
       <c r="B2414" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeMAY/16</t>
+          <t>New Home SalesAPR</t>
         </is>
       </c>
       <c r="C2414" t="inlineStr"/>
       <c r="D2414" t="inlineStr">
         <is>
-          <t>3.454M</t>
-        </is>
-      </c>
-      <c r="E2414" t="inlineStr"/>
-      <c r="F2414" t="inlineStr"/>
+          <t>0.724M</t>
+        </is>
+      </c>
+      <c r="E2414" t="inlineStr">
+        <is>
+          <t>0.69M</t>
+        </is>
+      </c>
+      <c r="F2414" t="inlineStr">
+        <is>
+          <t>0.69M</t>
+        </is>
+      </c>
       <c r="G2414" t="n">
         <v>2</v>
       </c>
@@ -68115,22 +68227,26 @@
     <row r="2415">
       <c r="A2415" t="inlineStr">
         <is>
-          <t>2025-05-21 20:00:00+05:30</t>
+          <t>2025-05-23 19:30:00+05:30</t>
         </is>
       </c>
       <c r="B2415" t="inlineStr">
         <is>
-          <t>EIA Crude Oil Stocks ChangeMAY/16</t>
+          <t>New Home Sales MoMAPR</t>
         </is>
       </c>
       <c r="C2415" t="inlineStr"/>
       <c r="D2415" t="inlineStr">
         <is>
-          <t>3.454M</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="E2415" t="inlineStr"/>
-      <c r="F2415" t="inlineStr"/>
+      <c r="F2415" t="inlineStr">
+        <is>
+          <t>-4.7%</t>
+        </is>
+      </c>
       <c r="G2415" t="n">
         <v>2</v>
       </c>
@@ -68138,45 +68254,49 @@
     <row r="2416">
       <c r="A2416" t="inlineStr">
         <is>
-          <t>2025-05-21 21:00:00+05:30</t>
+          <t>2025-05-23 21:30:00+05:30</t>
         </is>
       </c>
       <c r="B2416" t="inlineStr">
         <is>
-          <t>17-Week Bill Auction</t>
+          <t>Fed Cook Speech</t>
         </is>
       </c>
       <c r="C2416" t="inlineStr"/>
-      <c r="D2416" t="inlineStr">
-        <is>
-          <t>4.240%</t>
-        </is>
-      </c>
+      <c r="D2416" t="inlineStr"/>
       <c r="E2416" t="inlineStr"/>
       <c r="F2416" t="inlineStr"/>
       <c r="G2416" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2417">
       <c r="A2417" t="inlineStr">
         <is>
-          <t>2025-05-21 21:00:00+05:30</t>
+          <t>2025-05-23 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B2417" t="inlineStr">
         <is>
-          <t>17-Week Bill Auction</t>
+          <t>Building Permits FinalAPR</t>
         </is>
       </c>
       <c r="C2417" t="inlineStr"/>
       <c r="D2417" t="inlineStr">
         <is>
-          <t>4.240%</t>
-        </is>
-      </c>
-      <c r="E2417" t="inlineStr"/>
-      <c r="F2417" t="inlineStr"/>
+          <t>1.467M</t>
+        </is>
+      </c>
+      <c r="E2417" t="inlineStr">
+        <is>
+          <t>1.412M</t>
+        </is>
+      </c>
+      <c r="F2417" t="inlineStr">
+        <is>
+          <t>1.412M</t>
+        </is>
+      </c>
       <c r="G2417" t="n">
         <v>3</v>
       </c>
@@ -68184,60 +68304,76 @@
     <row r="2418">
       <c r="A2418" t="inlineStr">
         <is>
-          <t>2025-05-21 21:30:00+05:30</t>
+          <t>2025-05-23 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B2418" t="inlineStr">
         <is>
-          <t>Fed Barkin Speech</t>
+          <t>Baker Hughes Oil Rig CountMAY/23</t>
         </is>
       </c>
       <c r="C2418" t="inlineStr"/>
-      <c r="D2418" t="inlineStr"/>
+      <c r="D2418" t="inlineStr">
+        <is>
+          <t>473</t>
+        </is>
+      </c>
       <c r="E2418" t="inlineStr"/>
       <c r="F2418" t="inlineStr"/>
       <c r="G2418" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2419">
       <c r="A2419" t="inlineStr">
         <is>
-          <t>2025-05-21 21:30:00+05:30</t>
+          <t>2025-05-23 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B2419" t="inlineStr">
         <is>
-          <t>Fed Barkin Speech</t>
+          <t>Baker Hughes Total Rigs CountMAY/23</t>
         </is>
       </c>
       <c r="C2419" t="inlineStr"/>
-      <c r="D2419" t="inlineStr"/>
+      <c r="D2419" t="inlineStr">
+        <is>
+          <t>576</t>
+        </is>
+      </c>
       <c r="E2419" t="inlineStr"/>
       <c r="F2419" t="inlineStr"/>
       <c r="G2419" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2420">
       <c r="A2420" t="inlineStr">
         <is>
-          <t>2025-05-21 22:30:00+05:30</t>
+          <t>2025-05-23 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B2420" t="inlineStr">
         <is>
-          <t>20-Year Bond Auction</t>
+          <t>Building Permits MoM FinalAPR</t>
         </is>
       </c>
       <c r="C2420" t="inlineStr"/>
       <c r="D2420" t="inlineStr">
         <is>
-          <t>4.810%</t>
-        </is>
-      </c>
-      <c r="E2420" t="inlineStr"/>
-      <c r="F2420" t="inlineStr"/>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="E2420" t="inlineStr">
+        <is>
+          <t>-4.7%</t>
+        </is>
+      </c>
+      <c r="F2420" t="inlineStr">
+        <is>
+          <t>-4.7%</t>
+        </is>
+      </c>
       <c r="G2420" t="n">
         <v>3</v>
       </c>
@@ -68245,163 +68381,143 @@
     <row r="2421">
       <c r="A2421" t="inlineStr">
         <is>
-          <t>2025-05-21 22:30:00+05:30</t>
+          <t>2025-05-26 00:10:00+05:30</t>
         </is>
       </c>
       <c r="B2421" t="inlineStr">
         <is>
-          <t>20-Year Bond Auction</t>
+          <t>Fed Chair Powell Speech</t>
         </is>
       </c>
       <c r="C2421" t="inlineStr"/>
-      <c r="D2421" t="inlineStr">
-        <is>
-          <t>4.810%</t>
-        </is>
-      </c>
+      <c r="D2421" t="inlineStr"/>
       <c r="E2421" t="inlineStr"/>
       <c r="F2421" t="inlineStr"/>
       <c r="G2421" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2422">
       <c r="A2422" t="inlineStr">
         <is>
-          <t>2025-05-22 18:00:00+05:30</t>
+          <t>2025-05-27 13:30:00+05:30</t>
         </is>
       </c>
       <c r="B2422" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageMAY/17</t>
+          <t>Fed Kashkari Speech</t>
         </is>
       </c>
       <c r="C2422" t="inlineStr"/>
-      <c r="D2422" t="inlineStr">
-        <is>
-          <t>230.5K</t>
-        </is>
-      </c>
+      <c r="D2422" t="inlineStr"/>
       <c r="E2422" t="inlineStr"/>
-      <c r="F2422" t="inlineStr">
-        <is>
-          <t>231.0K</t>
-        </is>
-      </c>
+      <c r="F2422" t="inlineStr"/>
       <c r="G2422" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2423">
       <c r="A2423" t="inlineStr">
         <is>
-          <t>2025-05-22 18:00:00+05:30</t>
+          <t>2025-05-27 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B2423" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsMAY/10</t>
+          <t>Durable Goods Orders MoMAPR</t>
         </is>
       </c>
       <c r="C2423" t="inlineStr"/>
       <c r="D2423" t="inlineStr">
         <is>
-          <t>1881K</t>
-        </is>
-      </c>
-      <c r="E2423" t="inlineStr">
-        <is>
-          <t>1890K</t>
-        </is>
-      </c>
+          <t>7.5%</t>
+        </is>
+      </c>
+      <c r="E2423" t="inlineStr"/>
       <c r="F2423" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="G2423" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2424">
       <c r="A2424" t="inlineStr">
         <is>
-          <t>2025-05-22 18:00:00+05:30</t>
+          <t>2025-05-27 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B2424" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsMAY/17</t>
+          <t>Non Defense Goods Orders Ex AirAPR</t>
         </is>
       </c>
       <c r="C2424" t="inlineStr"/>
       <c r="D2424" t="inlineStr">
         <is>
-          <t>229K</t>
-        </is>
-      </c>
-      <c r="E2424" t="inlineStr">
-        <is>
-          <t>230K</t>
-        </is>
-      </c>
+          <t>-0.2%</t>
+        </is>
+      </c>
+      <c r="E2424" t="inlineStr"/>
       <c r="F2424" t="inlineStr">
         <is>
-          <t>231.0K</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G2424" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2425">
       <c r="A2425" t="inlineStr">
         <is>
-          <t>2025-05-22 18:00:00+05:30</t>
+          <t>2025-05-27 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B2425" t="inlineStr">
         <is>
-          <t>Chicago Fed National Activity IndexAPR</t>
+          <t>Durable Goods Orders ex Defense MoMAPR</t>
         </is>
       </c>
       <c r="C2425" t="inlineStr"/>
       <c r="D2425" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="E2425" t="inlineStr"/>
       <c r="F2425" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="G2425" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2426">
       <c r="A2426" t="inlineStr">
         <is>
-          <t>2025-05-22 18:00:00+05:30</t>
+          <t>2025-05-27 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B2426" t="inlineStr">
         <is>
-          <t>Chicago Fed National Activity IndexAPR</t>
+          <t>Durable Goods Orders Ex Transp MoMAPR</t>
         </is>
       </c>
       <c r="C2426" t="inlineStr"/>
       <c r="D2426" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="E2426" t="inlineStr"/>
       <c r="F2426" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="G2426" t="n">
@@ -68411,26 +68527,18 @@
     <row r="2427">
       <c r="A2427" t="inlineStr">
         <is>
-          <t>2025-05-22 18:00:00+05:30</t>
+          <t>2025-05-27 18:25:00+05:30</t>
         </is>
       </c>
       <c r="B2427" t="inlineStr">
         <is>
-          <t>Jobless Claims 4-week AverageMAY/17</t>
+          <t>Redbook YoYMAY/24</t>
         </is>
       </c>
       <c r="C2427" t="inlineStr"/>
-      <c r="D2427" t="inlineStr">
-        <is>
-          <t>230.5K</t>
-        </is>
-      </c>
+      <c r="D2427" t="inlineStr"/>
       <c r="E2427" t="inlineStr"/>
-      <c r="F2427" t="inlineStr">
-        <is>
-          <t>231.0K</t>
-        </is>
-      </c>
+      <c r="F2427" t="inlineStr"/>
       <c r="G2427" t="n">
         <v>3</v>
       </c>
@@ -68438,171 +68546,147 @@
     <row r="2428">
       <c r="A2428" t="inlineStr">
         <is>
-          <t>2025-05-22 18:00:00+05:30</t>
+          <t>2025-05-27 18:30:00+05:30</t>
         </is>
       </c>
       <c r="B2428" t="inlineStr">
         <is>
-          <t>Continuing Jobless ClaimsMAY/10</t>
+          <t>S&amp;P/Case-Shiller Home Price YoYMAR</t>
         </is>
       </c>
       <c r="C2428" t="inlineStr"/>
       <c r="D2428" t="inlineStr">
         <is>
-          <t>1881K</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="E2428" t="inlineStr"/>
       <c r="F2428" t="inlineStr">
         <is>
-          <t>1885.0K</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="G2428" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2429">
       <c r="A2429" t="inlineStr">
         <is>
-          <t>2025-05-22 18:00:00+05:30</t>
+          <t>2025-05-27 18:30:00+05:30</t>
         </is>
       </c>
       <c r="B2429" t="inlineStr">
         <is>
-          <t>Initial Jobless ClaimsMAY/17</t>
+          <t>S&amp;P/Case-Shiller Home Price MoMMAR</t>
         </is>
       </c>
       <c r="C2429" t="inlineStr"/>
       <c r="D2429" t="inlineStr">
         <is>
-          <t>229K</t>
-        </is>
-      </c>
-      <c r="E2429" t="inlineStr">
-        <is>
-          <t>232K</t>
-        </is>
-      </c>
+          <t>0.7%</t>
+        </is>
+      </c>
+      <c r="E2429" t="inlineStr"/>
       <c r="F2429" t="inlineStr">
         <is>
-          <t>231.0K</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="G2429" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2430">
       <c r="A2430" t="inlineStr">
         <is>
-          <t>2025-05-22 19:15:00+05:30</t>
+          <t>2025-05-27 18:30:00+05:30</t>
         </is>
       </c>
       <c r="B2430" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashMAY</t>
+          <t>House Price Index YoYMAR</t>
         </is>
       </c>
       <c r="C2430" t="inlineStr"/>
       <c r="D2430" t="inlineStr">
         <is>
-          <t>50.8</t>
-        </is>
-      </c>
-      <c r="E2430" t="inlineStr">
-        <is>
-          <t>51.5</t>
-        </is>
-      </c>
-      <c r="F2430" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>3.9%</t>
+        </is>
+      </c>
+      <c r="E2430" t="inlineStr"/>
+      <c r="F2430" t="inlineStr"/>
       <c r="G2430" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2431">
       <c r="A2431" t="inlineStr">
         <is>
-          <t>2025-05-22 19:15:00+05:30</t>
+          <t>2025-05-27 18:30:00+05:30</t>
         </is>
       </c>
       <c r="B2431" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashMAY</t>
+          <t>House Price IndexMAR</t>
         </is>
       </c>
       <c r="C2431" t="inlineStr"/>
       <c r="D2431" t="inlineStr">
         <is>
-          <t>50.2</t>
-        </is>
-      </c>
-      <c r="E2431" t="inlineStr">
-        <is>
-          <t>50.5</t>
-        </is>
-      </c>
-      <c r="F2431" t="inlineStr">
-        <is>
-          <t>50.3</t>
-        </is>
-      </c>
+          <t>437.3</t>
+        </is>
+      </c>
+      <c r="E2431" t="inlineStr"/>
+      <c r="F2431" t="inlineStr"/>
       <c r="G2431" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2432">
       <c r="A2432" t="inlineStr">
         <is>
-          <t>2025-05-22 19:15:00+05:30</t>
+          <t>2025-05-27 18:30:00+05:30</t>
         </is>
       </c>
       <c r="B2432" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashMAY</t>
+          <t>House Price Index MoMMAR</t>
         </is>
       </c>
       <c r="C2432" t="inlineStr"/>
       <c r="D2432" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="E2432" t="inlineStr"/>
-      <c r="F2432" t="inlineStr">
-        <is>
-          <t>50.4</t>
-        </is>
-      </c>
+      <c r="F2432" t="inlineStr"/>
       <c r="G2432" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2433">
       <c r="A2433" t="inlineStr">
         <is>
-          <t>2025-05-22 19:15:00+05:30</t>
+          <t>2025-05-27 19:30:00+05:30</t>
         </is>
       </c>
       <c r="B2433" t="inlineStr">
         <is>
-          <t>S&amp;P Global Composite PMI FlashMAY</t>
+          <t>CB Consumer ConfidenceMAY</t>
         </is>
       </c>
       <c r="C2433" t="inlineStr"/>
       <c r="D2433" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="E2433" t="inlineStr"/>
       <c r="F2433" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="G2433" t="n">
@@ -68612,28 +68696,24 @@
     <row r="2434">
       <c r="A2434" t="inlineStr">
         <is>
-          <t>2025-05-22 19:15:00+05:30</t>
+          <t>2025-05-27 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B2434" t="inlineStr">
         <is>
-          <t>S&amp;P Global Manufacturing PMI FlashMAY</t>
+          <t>Dallas Fed Manufacturing IndexMAY</t>
         </is>
       </c>
       <c r="C2434" t="inlineStr"/>
       <c r="D2434" t="inlineStr">
         <is>
-          <t>50.2</t>
-        </is>
-      </c>
-      <c r="E2434" t="inlineStr">
-        <is>
-          <t>50.5</t>
-        </is>
-      </c>
+          <t>-35.8</t>
+        </is>
+      </c>
+      <c r="E2434" t="inlineStr"/>
       <c r="F2434" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>-25</t>
         </is>
       </c>
       <c r="G2434" t="n">
@@ -68643,190 +68723,142 @@
     <row r="2435">
       <c r="A2435" t="inlineStr">
         <is>
-          <t>2025-05-22 19:15:00+05:30</t>
+          <t>2025-05-27 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B2435" t="inlineStr">
         <is>
-          <t>S&amp;P Global Services PMI FlashMAY</t>
+          <t>3-Month Bill Auction</t>
         </is>
       </c>
       <c r="C2435" t="inlineStr"/>
       <c r="D2435" t="inlineStr">
         <is>
-          <t>50.8</t>
-        </is>
-      </c>
-      <c r="E2435" t="inlineStr">
-        <is>
-          <t>51.5</t>
-        </is>
-      </c>
-      <c r="F2435" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
+          <t>4.285%</t>
+        </is>
+      </c>
+      <c r="E2435" t="inlineStr"/>
+      <c r="F2435" t="inlineStr"/>
       <c r="G2435" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2436">
       <c r="A2436" t="inlineStr">
         <is>
-          <t>2025-05-22 19:30:00+05:30</t>
+          <t>2025-05-27 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B2436" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMAPR</t>
+          <t>6-Month Bill Auction</t>
         </is>
       </c>
       <c r="C2436" t="inlineStr"/>
       <c r="D2436" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>4.140%</t>
         </is>
       </c>
       <c r="E2436" t="inlineStr"/>
-      <c r="F2436" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
+      <c r="F2436" t="inlineStr"/>
       <c r="G2436" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2437">
       <c r="A2437" t="inlineStr">
         <is>
-          <t>2025-05-22 19:30:00+05:30</t>
+          <t>2025-05-27 21:30:00+05:30</t>
         </is>
       </c>
       <c r="B2437" t="inlineStr">
         <is>
-          <t>Existing Home SalesAPR</t>
+          <t>2-Year Note Auction</t>
         </is>
       </c>
       <c r="C2437" t="inlineStr"/>
-      <c r="D2437" t="inlineStr">
-        <is>
-          <t>4.02M</t>
-        </is>
-      </c>
-      <c r="E2437" t="inlineStr">
-        <is>
-          <t>4.1M</t>
-        </is>
-      </c>
-      <c r="F2437" t="inlineStr">
-        <is>
-          <t>3.9M</t>
-        </is>
-      </c>
+      <c r="D2437" t="inlineStr"/>
+      <c r="E2437" t="inlineStr"/>
+      <c r="F2437" t="inlineStr"/>
       <c r="G2437" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2438">
       <c r="A2438" t="inlineStr">
         <is>
-          <t>2025-05-22 19:30:00+05:30</t>
+          <t>2025-05-27 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B2438" t="inlineStr">
         <is>
-          <t>Existing Home SalesAPR</t>
+          <t>Money SupplyAPR</t>
         </is>
       </c>
       <c r="C2438" t="inlineStr"/>
       <c r="D2438" t="inlineStr">
         <is>
-          <t>4.02M</t>
-        </is>
-      </c>
-      <c r="E2438" t="inlineStr">
-        <is>
-          <t>4.1M</t>
-        </is>
-      </c>
-      <c r="F2438" t="inlineStr">
-        <is>
-          <t>3.9M</t>
-        </is>
-      </c>
+          <t>$21.76T</t>
+        </is>
+      </c>
+      <c r="E2438" t="inlineStr"/>
+      <c r="F2438" t="inlineStr"/>
       <c r="G2438" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2439">
       <c r="A2439" t="inlineStr">
         <is>
-          <t>2025-05-22 19:30:00+05:30</t>
+          <t>2025-05-28 16:30:00+05:30</t>
         </is>
       </c>
       <c r="B2439" t="inlineStr">
         <is>
-          <t>Existing Home Sales MoMAPR</t>
+          <t>MBA Mortgage Refinance IndexMAY/23</t>
         </is>
       </c>
       <c r="C2439" t="inlineStr"/>
-      <c r="D2439" t="inlineStr">
-        <is>
-          <t>-5.9%</t>
-        </is>
-      </c>
+      <c r="D2439" t="inlineStr"/>
       <c r="E2439" t="inlineStr"/>
-      <c r="F2439" t="inlineStr">
-        <is>
-          <t>-3%</t>
-        </is>
-      </c>
+      <c r="F2439" t="inlineStr"/>
       <c r="G2439" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2440">
       <c r="A2440" t="inlineStr">
         <is>
-          <t>2025-05-22 20:00:00+05:30</t>
+          <t>2025-05-28 16:30:00+05:30</t>
         </is>
       </c>
       <c r="B2440" t="inlineStr">
         <is>
-          <t>EIA Natural Gas Stocks ChangeMAY/16</t>
+          <t>MBA 30-Year Mortgage RateMAY/23</t>
         </is>
       </c>
       <c r="C2440" t="inlineStr"/>
-      <c r="D2440" t="inlineStr">
-        <is>
-          <t>110Bcf</t>
-        </is>
-      </c>
+      <c r="D2440" t="inlineStr"/>
       <c r="E2440" t="inlineStr"/>
       <c r="F2440" t="inlineStr"/>
       <c r="G2440" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2441">
       <c r="A2441" t="inlineStr">
         <is>
-          <t>2025-05-22 20:00:00+05:30</t>
+          <t>2025-05-28 16:30:00+05:30</t>
         </is>
       </c>
       <c r="B2441" t="inlineStr">
         <is>
-          <t>EIA Natural Gas Stocks ChangeMAY/16</t>
+          <t>MBA Mortgage ApplicationsMAY/23</t>
         </is>
       </c>
       <c r="C2441" t="inlineStr"/>
-      <c r="D2441" t="inlineStr">
-        <is>
-          <t>110Bcf</t>
-        </is>
-      </c>
+      <c r="D2441" t="inlineStr"/>
       <c r="E2441" t="inlineStr"/>
       <c r="F2441" t="inlineStr"/>
       <c r="G2441" t="n">
@@ -68836,26 +68868,18 @@
     <row r="2442">
       <c r="A2442" t="inlineStr">
         <is>
-          <t>2025-05-22 20:30:00+05:30</t>
+          <t>2025-05-28 16:30:00+05:30</t>
         </is>
       </c>
       <c r="B2442" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexMAY</t>
+          <t>MBA Mortgage Market IndexMAY/23</t>
         </is>
       </c>
       <c r="C2442" t="inlineStr"/>
-      <c r="D2442" t="inlineStr">
-        <is>
-          <t>-4</t>
-        </is>
-      </c>
+      <c r="D2442" t="inlineStr"/>
       <c r="E2442" t="inlineStr"/>
-      <c r="F2442" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
-      </c>
+      <c r="F2442" t="inlineStr"/>
       <c r="G2442" t="n">
         <v>3</v>
       </c>
@@ -68863,26 +68887,18 @@
     <row r="2443">
       <c r="A2443" t="inlineStr">
         <is>
-          <t>2025-05-22 20:30:00+05:30</t>
+          <t>2025-05-28 16:30:00+05:30</t>
         </is>
       </c>
       <c r="B2443" t="inlineStr">
         <is>
-          <t>Kansas Fed Composite IndexMAY</t>
+          <t>MBA Purchase IndexMAY/23</t>
         </is>
       </c>
       <c r="C2443" t="inlineStr"/>
-      <c r="D2443" t="inlineStr">
-        <is>
-          <t>-4</t>
-        </is>
-      </c>
+      <c r="D2443" t="inlineStr"/>
       <c r="E2443" t="inlineStr"/>
-      <c r="F2443" t="inlineStr">
-        <is>
-          <t>-3</t>
-        </is>
-      </c>
+      <c r="F2443" t="inlineStr"/>
       <c r="G2443" t="n">
         <v>3</v>
       </c>
@@ -68890,24 +68906,24 @@
     <row r="2444">
       <c r="A2444" t="inlineStr">
         <is>
-          <t>2025-05-22 20:30:00+05:30</t>
+          <t>2025-05-28 19:30:00+05:30</t>
         </is>
       </c>
       <c r="B2444" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexMAY</t>
+          <t>Richmond Fed Services Revenues IndexMAY</t>
         </is>
       </c>
       <c r="C2444" t="inlineStr"/>
       <c r="D2444" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="E2444" t="inlineStr"/>
       <c r="F2444" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="G2444" t="n">
@@ -68917,24 +68933,24 @@
     <row r="2445">
       <c r="A2445" t="inlineStr">
         <is>
-          <t>2025-05-22 20:30:00+05:30</t>
+          <t>2025-05-28 19:30:00+05:30</t>
         </is>
       </c>
       <c r="B2445" t="inlineStr">
         <is>
-          <t>Kansas Fed Manufacturing IndexMAY</t>
+          <t>Richmond Fed Manufacturing Shipments IndexMAY</t>
         </is>
       </c>
       <c r="C2445" t="inlineStr"/>
       <c r="D2445" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-17</t>
         </is>
       </c>
       <c r="E2445" t="inlineStr"/>
       <c r="F2445" t="inlineStr">
         <is>
-          <t>-1</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="G2445" t="n">
@@ -68944,22 +68960,26 @@
     <row r="2446">
       <c r="A2446" t="inlineStr">
         <is>
-          <t>2025-05-22 21:00:00+05:30</t>
+          <t>2025-05-28 19:30:00+05:30</t>
         </is>
       </c>
       <c r="B2446" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>Richmond Fed Manufacturing IndexMAY</t>
         </is>
       </c>
       <c r="C2446" t="inlineStr"/>
       <c r="D2446" t="inlineStr">
         <is>
-          <t>4.22%</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="E2446" t="inlineStr"/>
-      <c r="F2446" t="inlineStr"/>
+      <c r="F2446" t="inlineStr">
+        <is>
+          <t>-11</t>
+        </is>
+      </c>
       <c r="G2446" t="n">
         <v>3</v>
       </c>
@@ -68967,22 +68987,26 @@
     <row r="2447">
       <c r="A2447" t="inlineStr">
         <is>
-          <t>2025-05-22 21:00:00+05:30</t>
+          <t>2025-05-28 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B2447" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>Dallas Fed Services IndexMAY</t>
         </is>
       </c>
       <c r="C2447" t="inlineStr"/>
       <c r="D2447" t="inlineStr">
         <is>
-          <t>4.235%</t>
+          <t>-19.4</t>
         </is>
       </c>
       <c r="E2447" t="inlineStr"/>
-      <c r="F2447" t="inlineStr"/>
+      <c r="F2447" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
       <c r="G2447" t="n">
         <v>3</v>
       </c>
@@ -68990,22 +69014,26 @@
     <row r="2448">
       <c r="A2448" t="inlineStr">
         <is>
-          <t>2025-05-22 21:00:00+05:30</t>
+          <t>2025-05-28 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B2448" t="inlineStr">
         <is>
-          <t>4-Week Bill Auction</t>
+          <t>Dallas Fed Services Revenues IndexMAY</t>
         </is>
       </c>
       <c r="C2448" t="inlineStr"/>
       <c r="D2448" t="inlineStr">
         <is>
-          <t>4.22%</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="E2448" t="inlineStr"/>
-      <c r="F2448" t="inlineStr"/>
+      <c r="F2448" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="G2448" t="n">
         <v>3</v>
       </c>
@@ -69013,20 +69041,16 @@
     <row r="2449">
       <c r="A2449" t="inlineStr">
         <is>
-          <t>2025-05-22 21:00:00+05:30</t>
+          <t>2025-05-28 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B2449" t="inlineStr">
         <is>
-          <t>8-Week Bill Auction</t>
+          <t>17-Week Bill Auction</t>
         </is>
       </c>
       <c r="C2449" t="inlineStr"/>
-      <c r="D2449" t="inlineStr">
-        <is>
-          <t>4.235%</t>
-        </is>
-      </c>
+      <c r="D2449" t="inlineStr"/>
       <c r="E2449" t="inlineStr"/>
       <c r="F2449" t="inlineStr"/>
       <c r="G2449" t="n">
@@ -69036,18 +69060,18 @@
     <row r="2450">
       <c r="A2450" t="inlineStr">
         <is>
-          <t>2025-05-22 21:30:00+05:30</t>
+          <t>2025-05-28 21:30:00+05:30</t>
         </is>
       </c>
       <c r="B2450" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateMAY/22</t>
+          <t>5-Year Note Auction</t>
         </is>
       </c>
       <c r="C2450" t="inlineStr"/>
       <c r="D2450" t="inlineStr">
         <is>
-          <t>5.92%</t>
+          <t>3.995%</t>
         </is>
       </c>
       <c r="E2450" t="inlineStr"/>
@@ -69059,18 +69083,18 @@
     <row r="2451">
       <c r="A2451" t="inlineStr">
         <is>
-          <t>2025-05-22 21:30:00+05:30</t>
+          <t>2025-05-28 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B2451" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateMAY/22</t>
+          <t>2-Year FRN Auction</t>
         </is>
       </c>
       <c r="C2451" t="inlineStr"/>
       <c r="D2451" t="inlineStr">
         <is>
-          <t>6.81%</t>
+          <t>0.160%</t>
         </is>
       </c>
       <c r="E2451" t="inlineStr"/>
@@ -69082,91 +69106,95 @@
     <row r="2452">
       <c r="A2452" t="inlineStr">
         <is>
-          <t>2025-05-22 21:30:00+05:30</t>
+          <t>2025-05-28 23:30:00+05:30</t>
         </is>
       </c>
       <c r="B2452" t="inlineStr">
         <is>
-          <t>10-Year TIPS Auction</t>
+          <t>FOMC Minutes</t>
         </is>
       </c>
       <c r="C2452" t="inlineStr"/>
-      <c r="D2452" t="inlineStr">
-        <is>
-          <t>1.935%</t>
-        </is>
-      </c>
+      <c r="D2452" t="inlineStr"/>
       <c r="E2452" t="inlineStr"/>
       <c r="F2452" t="inlineStr"/>
       <c r="G2452" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2453">
       <c r="A2453" t="inlineStr">
         <is>
-          <t>2025-05-22 21:30:00+05:30</t>
+          <t>2025-05-29 02:00:00+05:30</t>
         </is>
       </c>
       <c r="B2453" t="inlineStr">
         <is>
-          <t>30-Year Mortgage RateMAY/22</t>
+          <t>API Crude Oil Stock ChangeMAY/23</t>
         </is>
       </c>
       <c r="C2453" t="inlineStr"/>
-      <c r="D2453" t="inlineStr">
-        <is>
-          <t>6.81%</t>
-        </is>
-      </c>
+      <c r="D2453" t="inlineStr"/>
       <c r="E2453" t="inlineStr"/>
       <c r="F2453" t="inlineStr"/>
       <c r="G2453" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2454">
       <c r="A2454" t="inlineStr">
         <is>
-          <t>2025-05-22 21:30:00+05:30</t>
+          <t>2025-05-29 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B2454" t="inlineStr">
         <is>
-          <t>15-Year Mortgage RateMAY/22</t>
+          <t>GDP Growth Rate QoQ 2nd EstQ1</t>
         </is>
       </c>
       <c r="C2454" t="inlineStr"/>
       <c r="D2454" t="inlineStr">
         <is>
-          <t>5.92%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="E2454" t="inlineStr"/>
-      <c r="F2454" t="inlineStr"/>
+      <c r="F2454" t="inlineStr">
+        <is>
+          <t>-0.3%</t>
+        </is>
+      </c>
       <c r="G2454" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2455">
       <c r="A2455" t="inlineStr">
         <is>
-          <t>2025-05-22 22:30:00+05:30</t>
+          <t>2025-05-29 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B2455" t="inlineStr">
         <is>
-          <t>10-Year TIPS Auction</t>
+          <t>GDP Sales QoQ 2nd EstQ1</t>
         </is>
       </c>
       <c r="C2455" t="inlineStr"/>
       <c r="D2455" t="inlineStr">
         <is>
-          <t>1.935%</t>
-        </is>
-      </c>
-      <c r="E2455" t="inlineStr"/>
-      <c r="F2455" t="inlineStr"/>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="E2455" t="inlineStr">
+        <is>
+          <t>-2.5%</t>
+        </is>
+      </c>
+      <c r="F2455" t="inlineStr">
+        <is>
+          <t>-2.5%</t>
+        </is>
+      </c>
       <c r="G2455" t="n">
         <v>3</v>
       </c>
@@ -69174,60 +69202,76 @@
     <row r="2456">
       <c r="A2456" t="inlineStr">
         <is>
-          <t>2025-05-22 22:30:00+05:30</t>
+          <t>2025-05-29 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B2456" t="inlineStr">
         <is>
-          <t>10-Year TIPS Auction</t>
+          <t>Initial Jobless ClaimsMAY/24</t>
         </is>
       </c>
       <c r="C2456" t="inlineStr"/>
-      <c r="D2456" t="inlineStr">
-        <is>
-          <t>1.935%</t>
-        </is>
-      </c>
+      <c r="D2456" t="inlineStr"/>
       <c r="E2456" t="inlineStr"/>
       <c r="F2456" t="inlineStr"/>
       <c r="G2456" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2457">
       <c r="A2457" t="inlineStr">
         <is>
-          <t>2025-05-22 23:30:00+05:30</t>
+          <t>2025-05-29 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B2457" t="inlineStr">
         <is>
-          <t>Fed Williams Speech</t>
+          <t>PCE Prices QoQ 2nd EstQ1</t>
         </is>
       </c>
       <c r="C2457" t="inlineStr"/>
-      <c r="D2457" t="inlineStr"/>
-      <c r="E2457" t="inlineStr"/>
-      <c r="F2457" t="inlineStr"/>
+      <c r="D2457" t="inlineStr">
+        <is>
+          <t>2.4%</t>
+        </is>
+      </c>
+      <c r="E2457" t="inlineStr">
+        <is>
+          <t>3.6%</t>
+        </is>
+      </c>
+      <c r="F2457" t="inlineStr">
+        <is>
+          <t>3.6%</t>
+        </is>
+      </c>
       <c r="G2457" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2458">
       <c r="A2458" t="inlineStr">
         <is>
-          <t>2025-05-22 23:30:00+05:30</t>
+          <t>2025-05-29 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B2458" t="inlineStr">
         <is>
-          <t>Fed Williams Speech</t>
+          <t>Corporate Profits QoQ PrelQ1</t>
         </is>
       </c>
       <c r="C2458" t="inlineStr"/>
-      <c r="D2458" t="inlineStr"/>
+      <c r="D2458" t="inlineStr">
+        <is>
+          <t>5.9%</t>
+        </is>
+      </c>
       <c r="E2458" t="inlineStr"/>
-      <c r="F2458" t="inlineStr"/>
+      <c r="F2458" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
+      </c>
       <c r="G2458" t="n">
         <v>2</v>
       </c>
@@ -69235,20 +69279,16 @@
     <row r="2459">
       <c r="A2459" t="inlineStr">
         <is>
-          <t>2025-05-23 02:00:00+05:30</t>
+          <t>2025-05-29 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B2459" t="inlineStr">
         <is>
-          <t>Fed Balance SheetMAY/21</t>
+          <t>Jobless Claims 4-week AverageMAY/24</t>
         </is>
       </c>
       <c r="C2459" t="inlineStr"/>
-      <c r="D2459" t="inlineStr">
-        <is>
-          <t>$6.71T</t>
-        </is>
-      </c>
+      <c r="D2459" t="inlineStr"/>
       <c r="E2459" t="inlineStr"/>
       <c r="F2459" t="inlineStr"/>
       <c r="G2459" t="n">
@@ -69258,22 +69298,30 @@
     <row r="2460">
       <c r="A2460" t="inlineStr">
         <is>
-          <t>2025-05-23 02:00:00+05:30</t>
+          <t>2025-05-29 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B2460" t="inlineStr">
         <is>
-          <t>Building Permits FinalAPR</t>
+          <t>Core PCE Prices QoQ 2nd EstQ1</t>
         </is>
       </c>
       <c r="C2460" t="inlineStr"/>
       <c r="D2460" t="inlineStr">
         <is>
-          <t>1.467M</t>
-        </is>
-      </c>
-      <c r="E2460" t="inlineStr"/>
-      <c r="F2460" t="inlineStr"/>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="E2460" t="inlineStr">
+        <is>
+          <t>3.5%</t>
+        </is>
+      </c>
+      <c r="F2460" t="inlineStr">
+        <is>
+          <t>3.5%</t>
+        </is>
+      </c>
       <c r="G2460" t="n">
         <v>3</v>
       </c>
@@ -69281,20 +69329,16 @@
     <row r="2461">
       <c r="A2461" t="inlineStr">
         <is>
-          <t>2025-05-23 02:00:00+05:30</t>
+          <t>2025-05-29 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B2461" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalAPR</t>
+          <t>Continuing Jobless ClaimsMAY/17</t>
         </is>
       </c>
       <c r="C2461" t="inlineStr"/>
-      <c r="D2461" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+      <c r="D2461" t="inlineStr"/>
       <c r="E2461" t="inlineStr"/>
       <c r="F2461" t="inlineStr"/>
       <c r="G2461" t="n">
@@ -69304,45 +69348,57 @@
     <row r="2462">
       <c r="A2462" t="inlineStr">
         <is>
-          <t>2025-05-23 02:00:00+05:30</t>
+          <t>2025-05-29 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B2462" t="inlineStr">
         <is>
-          <t>Fed Balance SheetMAY/21</t>
+          <t>GDP Price Index QoQ 2nd EstQ1</t>
         </is>
       </c>
       <c r="C2462" t="inlineStr"/>
       <c r="D2462" t="inlineStr">
         <is>
-          <t>$6.71T</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E2462" t="inlineStr"/>
-      <c r="F2462" t="inlineStr"/>
+      <c r="F2462" t="inlineStr">
+        <is>
+          <t>3.7%</t>
+        </is>
+      </c>
       <c r="G2462" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2463">
       <c r="A2463" t="inlineStr">
         <is>
-          <t>2025-05-23 19:30:00+05:30</t>
+          <t>2025-05-29 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B2463" t="inlineStr">
         <is>
-          <t>Building Permits FinalAPR</t>
+          <t>Real Consumer Spending QoQ 2nd EstQ1</t>
         </is>
       </c>
       <c r="C2463" t="inlineStr"/>
       <c r="D2463" t="inlineStr">
         <is>
-          <t>1.467M</t>
-        </is>
-      </c>
-      <c r="E2463" t="inlineStr"/>
-      <c r="F2463" t="inlineStr"/>
+          <t>4%</t>
+        </is>
+      </c>
+      <c r="E2463" t="inlineStr">
+        <is>
+          <t>1.8%</t>
+        </is>
+      </c>
+      <c r="F2463" t="inlineStr">
+        <is>
+          <t>1.8%</t>
+        </is>
+      </c>
       <c r="G2463" t="n">
         <v>3</v>
       </c>
@@ -69350,26 +69406,18 @@
     <row r="2464">
       <c r="A2464" t="inlineStr">
         <is>
-          <t>2025-05-23 19:30:00+05:30</t>
+          <t>2025-05-29 19:30:00+05:30</t>
         </is>
       </c>
       <c r="B2464" t="inlineStr">
         <is>
-          <t>New Home Sales MoMAPR</t>
+          <t>Pending Home Sales YoYAPR</t>
         </is>
       </c>
       <c r="C2464" t="inlineStr"/>
-      <c r="D2464" t="inlineStr">
-        <is>
-          <t>7.4%</t>
-        </is>
-      </c>
+      <c r="D2464" t="inlineStr"/>
       <c r="E2464" t="inlineStr"/>
-      <c r="F2464" t="inlineStr">
-        <is>
-          <t>-4.7%</t>
-        </is>
-      </c>
+      <c r="F2464" t="inlineStr"/>
       <c r="G2464" t="n">
         <v>2</v>
       </c>
@@ -69377,28 +69425,24 @@
     <row r="2465">
       <c r="A2465" t="inlineStr">
         <is>
-          <t>2025-05-23 19:30:00+05:30</t>
+          <t>2025-05-29 19:30:00+05:30</t>
         </is>
       </c>
       <c r="B2465" t="inlineStr">
         <is>
-          <t>New Home SalesAPR</t>
+          <t>Pending Home Sales MoMAPR</t>
         </is>
       </c>
       <c r="C2465" t="inlineStr"/>
       <c r="D2465" t="inlineStr">
         <is>
-          <t>0.724M</t>
-        </is>
-      </c>
-      <c r="E2465" t="inlineStr">
-        <is>
-          <t>0.69M</t>
-        </is>
-      </c>
+          <t>6.1%</t>
+        </is>
+      </c>
+      <c r="E2465" t="inlineStr"/>
       <c r="F2465" t="inlineStr">
         <is>
-          <t>0.69M</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="G2465" t="n">
@@ -69408,20 +69452,16 @@
     <row r="2466">
       <c r="A2466" t="inlineStr">
         <is>
-          <t>2025-05-23 19:30:00+05:30</t>
+          <t>2025-05-29 20:00:00+05:30</t>
         </is>
       </c>
       <c r="B2466" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalAPR</t>
+          <t>EIA Natural Gas Stocks ChangeMAY/23</t>
         </is>
       </c>
       <c r="C2466" t="inlineStr"/>
-      <c r="D2466" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
+      <c r="D2466" t="inlineStr"/>
       <c r="E2466" t="inlineStr"/>
       <c r="F2466" t="inlineStr"/>
       <c r="G2466" t="n">
@@ -69431,30 +69471,18 @@
     <row r="2467">
       <c r="A2467" t="inlineStr">
         <is>
-          <t>2025-05-23 19:30:00+05:30</t>
+          <t>2025-05-29 20:10:00+05:30</t>
         </is>
       </c>
       <c r="B2467" t="inlineStr">
         <is>
-          <t>New Home SalesAPR</t>
+          <t>Fed Goolsbee Speech</t>
         </is>
       </c>
       <c r="C2467" t="inlineStr"/>
-      <c r="D2467" t="inlineStr">
-        <is>
-          <t>0.724M</t>
-        </is>
-      </c>
-      <c r="E2467" t="inlineStr">
-        <is>
-          <t>0.69M</t>
-        </is>
-      </c>
-      <c r="F2467" t="inlineStr">
-        <is>
-          <t>0.69M</t>
-        </is>
-      </c>
+      <c r="D2467" t="inlineStr"/>
+      <c r="E2467" t="inlineStr"/>
+      <c r="F2467" t="inlineStr"/>
       <c r="G2467" t="n">
         <v>2</v>
       </c>
@@ -69462,39 +69490,31 @@
     <row r="2468">
       <c r="A2468" t="inlineStr">
         <is>
-          <t>2025-05-23 19:30:00+05:30</t>
+          <t>2025-05-29 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B2468" t="inlineStr">
         <is>
-          <t>New Home Sales MoMAPR</t>
+          <t>EIA Crude Oil Imports ChangeMAY/23</t>
         </is>
       </c>
       <c r="C2468" t="inlineStr"/>
-      <c r="D2468" t="inlineStr">
-        <is>
-          <t>7.4%</t>
-        </is>
-      </c>
+      <c r="D2468" t="inlineStr"/>
       <c r="E2468" t="inlineStr"/>
-      <c r="F2468" t="inlineStr">
-        <is>
-          <t>-4.7%</t>
-        </is>
-      </c>
+      <c r="F2468" t="inlineStr"/>
       <c r="G2468" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2469">
       <c r="A2469" t="inlineStr">
         <is>
-          <t>2025-05-23 21:30:00+05:30</t>
+          <t>2025-05-29 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B2469" t="inlineStr">
         <is>
-          <t>Fed Cook Speech</t>
+          <t>EIA Gasoline Production ChangeMAY/23</t>
         </is>
       </c>
       <c r="C2469" t="inlineStr"/>
@@ -69502,18 +69522,18 @@
       <c r="E2469" t="inlineStr"/>
       <c r="F2469" t="inlineStr"/>
       <c r="G2469" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2470">
       <c r="A2470" t="inlineStr">
         <is>
-          <t>2025-05-23 21:30:00+05:30</t>
+          <t>2025-05-29 20:30:00+05:30</t>
         </is>
       </c>
       <c r="B2470" t="inlineStr">
         <is>
-          <t>Fed Cook Speech</t>
+          <t>EIA Distillate Stocks ChangeMAY/23</t>
         </is>
       </c>
       <c r="C2470" t="inlineStr"/>
@@ -69521,26 +69541,22 @@
       <c r="E2470" t="inlineStr"/>
       <c r="F2470" t="inlineStr"/>
       <c r="G2470" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2471">
       <c r="A2471" t="inlineStr">
         <is>
-          <t>2025-05-23 22:30:00+05:30</t>
+          <t>2025-05-29 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B2471" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountMAY/23</t>
+          <t>4-Week Bill Auction</t>
         </is>
       </c>
       <c r="C2471" t="inlineStr"/>
-      <c r="D2471" t="inlineStr">
-        <is>
-          <t>576</t>
-        </is>
-      </c>
+      <c r="D2471" t="inlineStr"/>
       <c r="E2471" t="inlineStr"/>
       <c r="F2471" t="inlineStr"/>
       <c r="G2471" t="n">
@@ -69550,20 +69566,16 @@
     <row r="2472">
       <c r="A2472" t="inlineStr">
         <is>
-          <t>2025-05-23 22:30:00+05:30</t>
+          <t>2025-05-29 21:00:00+05:30</t>
         </is>
       </c>
       <c r="B2472" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountMAY/23</t>
+          <t>8-Week Bill Auction</t>
         </is>
       </c>
       <c r="C2472" t="inlineStr"/>
-      <c r="D2472" t="inlineStr">
-        <is>
-          <t>473</t>
-        </is>
-      </c>
+      <c r="D2472" t="inlineStr"/>
       <c r="E2472" t="inlineStr"/>
       <c r="F2472" t="inlineStr"/>
       <c r="G2472" t="n">
@@ -69573,61 +69585,37 @@
     <row r="2473">
       <c r="A2473" t="inlineStr">
         <is>
-          <t>2025-05-23 22:30:00+05:30</t>
+          <t>2025-05-29 21:30:00+05:30</t>
         </is>
       </c>
       <c r="B2473" t="inlineStr">
         <is>
-          <t>Building Permits FinalAPR</t>
+          <t>EIA Gasoline Stocks ChangeMAY/23</t>
         </is>
       </c>
       <c r="C2473" t="inlineStr"/>
-      <c r="D2473" t="inlineStr">
-        <is>
-          <t>1.467M</t>
-        </is>
-      </c>
-      <c r="E2473" t="inlineStr">
-        <is>
-          <t>1.412M</t>
-        </is>
-      </c>
-      <c r="F2473" t="inlineStr">
-        <is>
-          <t>1.412M</t>
-        </is>
-      </c>
+      <c r="D2473" t="inlineStr"/>
+      <c r="E2473" t="inlineStr"/>
+      <c r="F2473" t="inlineStr"/>
       <c r="G2473" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2474">
       <c r="A2474" t="inlineStr">
         <is>
-          <t>2025-05-23 22:30:00+05:30</t>
+          <t>2025-05-29 21:30:00+05:30</t>
         </is>
       </c>
       <c r="B2474" t="inlineStr">
         <is>
-          <t>Building Permits FinalAPR</t>
+          <t>EIA Refinery Crude Runs ChangeMAY/23</t>
         </is>
       </c>
       <c r="C2474" t="inlineStr"/>
-      <c r="D2474" t="inlineStr">
-        <is>
-          <t>1.467M</t>
-        </is>
-      </c>
-      <c r="E2474" t="inlineStr">
-        <is>
-          <t>1.412M</t>
-        </is>
-      </c>
-      <c r="F2474" t="inlineStr">
-        <is>
-          <t>1.412M</t>
-        </is>
-      </c>
+      <c r="D2474" t="inlineStr"/>
+      <c r="E2474" t="inlineStr"/>
+      <c r="F2474" t="inlineStr"/>
       <c r="G2474" t="n">
         <v>3</v>
       </c>
@@ -69635,30 +69623,18 @@
     <row r="2475">
       <c r="A2475" t="inlineStr">
         <is>
-          <t>2025-05-23 22:30:00+05:30</t>
+          <t>2025-05-29 21:30:00+05:30</t>
         </is>
       </c>
       <c r="B2475" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalAPR</t>
+          <t>EIA Heating Oil Stocks ChangeMAY/23</t>
         </is>
       </c>
       <c r="C2475" t="inlineStr"/>
-      <c r="D2475" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E2475" t="inlineStr">
-        <is>
-          <t>-4.7%</t>
-        </is>
-      </c>
-      <c r="F2475" t="inlineStr">
-        <is>
-          <t>-4.7%</t>
-        </is>
-      </c>
+      <c r="D2475" t="inlineStr"/>
+      <c r="E2475" t="inlineStr"/>
+      <c r="F2475" t="inlineStr"/>
       <c r="G2475" t="n">
         <v>3</v>
       </c>
@@ -69666,20 +69642,16 @@
     <row r="2476">
       <c r="A2476" t="inlineStr">
         <is>
-          <t>2025-05-23 22:30:00+05:30</t>
+          <t>2025-05-29 21:30:00+05:30</t>
         </is>
       </c>
       <c r="B2476" t="inlineStr">
         <is>
-          <t>Baker Hughes Oil Rig CountMAY/23</t>
+          <t>EIA Distillate Fuel Production ChangeMAY/23</t>
         </is>
       </c>
       <c r="C2476" t="inlineStr"/>
-      <c r="D2476" t="inlineStr">
-        <is>
-          <t>473</t>
-        </is>
-      </c>
+      <c r="D2476" t="inlineStr"/>
       <c r="E2476" t="inlineStr"/>
       <c r="F2476" t="inlineStr"/>
       <c r="G2476" t="n">
@@ -69689,20 +69661,16 @@
     <row r="2477">
       <c r="A2477" t="inlineStr">
         <is>
-          <t>2025-05-23 22:30:00+05:30</t>
+          <t>2025-05-29 21:30:00+05:30</t>
         </is>
       </c>
       <c r="B2477" t="inlineStr">
         <is>
-          <t>Baker Hughes Total Rigs CountMAY/23</t>
+          <t>EIA Cushing Crude Oil Stocks ChangeMAY/23</t>
         </is>
       </c>
       <c r="C2477" t="inlineStr"/>
-      <c r="D2477" t="inlineStr">
-        <is>
-          <t>576</t>
-        </is>
-      </c>
+      <c r="D2477" t="inlineStr"/>
       <c r="E2477" t="inlineStr"/>
       <c r="F2477" t="inlineStr"/>
       <c r="G2477" t="n">
@@ -69712,30 +69680,18 @@
     <row r="2478">
       <c r="A2478" t="inlineStr">
         <is>
-          <t>2025-05-23 22:30:00+05:30</t>
+          <t>2025-05-29 21:30:00+05:30</t>
         </is>
       </c>
       <c r="B2478" t="inlineStr">
         <is>
-          <t>Building Permits MoM FinalAPR</t>
+          <t>7-Year Note Auction</t>
         </is>
       </c>
       <c r="C2478" t="inlineStr"/>
-      <c r="D2478" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E2478" t="inlineStr">
-        <is>
-          <t>-4.7%</t>
-        </is>
-      </c>
-      <c r="F2478" t="inlineStr">
-        <is>
-          <t>-4.7%</t>
-        </is>
-      </c>
+      <c r="D2478" t="inlineStr"/>
+      <c r="E2478" t="inlineStr"/>
+      <c r="F2478" t="inlineStr"/>
       <c r="G2478" t="n">
         <v>3</v>
       </c>
@@ -69743,12 +69699,12 @@
     <row r="2479">
       <c r="A2479" t="inlineStr">
         <is>
-          <t>2025-05-26 00:10:00+05:30</t>
+          <t>2025-05-29 21:30:00+05:30</t>
         </is>
       </c>
       <c r="B2479" t="inlineStr">
         <is>
-          <t>Fed Chair Powell Speech</t>
+          <t>30-Year Mortgage RateMAY/29</t>
         </is>
       </c>
       <c r="C2479" t="inlineStr"/>
@@ -69756,18 +69712,18 @@
       <c r="E2479" t="inlineStr"/>
       <c r="F2479" t="inlineStr"/>
       <c r="G2479" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2480">
       <c r="A2480" t="inlineStr">
         <is>
-          <t>2025-05-26 00:10:00+05:30</t>
+          <t>2025-05-29 21:30:00+05:30</t>
         </is>
       </c>
       <c r="B2480" t="inlineStr">
         <is>
-          <t>Fed Chair Powell Speech</t>
+          <t>EIA Crude Oil Stocks ChangeMAY/23</t>
         </is>
       </c>
       <c r="C2480" t="inlineStr"/>
@@ -69781,12 +69737,12 @@
     <row r="2481">
       <c r="A2481" t="inlineStr">
         <is>
-          <t>2025-05-27 13:30:00+05:30</t>
+          <t>2025-05-29 21:30:00+05:30</t>
         </is>
       </c>
       <c r="B2481" t="inlineStr">
         <is>
-          <t>Fed Kashkari Speech</t>
+          <t>15-Year Mortgage RateMAY/29</t>
         </is>
       </c>
       <c r="C2481" t="inlineStr"/>
@@ -69794,18 +69750,18 @@
       <c r="E2481" t="inlineStr"/>
       <c r="F2481" t="inlineStr"/>
       <c r="G2481" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2482">
       <c r="A2482" t="inlineStr">
         <is>
-          <t>2025-05-27 13:30:00+05:30</t>
+          <t>2025-05-30 02:00:00+05:30</t>
         </is>
       </c>
       <c r="B2482" t="inlineStr">
         <is>
-          <t>Fed Kashkari Speech</t>
+          <t>Fed Balance SheetMAY/28</t>
         </is>
       </c>
       <c r="C2482" t="inlineStr"/>
@@ -69813,167 +69769,143 @@
       <c r="E2482" t="inlineStr"/>
       <c r="F2482" t="inlineStr"/>
       <c r="G2482" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2483">
       <c r="A2483" t="inlineStr">
         <is>
-          <t>2025-05-27 18:00:00+05:30</t>
+          <t>2025-05-30 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B2483" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMAPR</t>
+          <t>Retail Inventories Ex Autos MoM AdvAPR</t>
         </is>
       </c>
       <c r="C2483" t="inlineStr"/>
-      <c r="D2483" t="inlineStr">
-        <is>
-          <t>8.9%</t>
-        </is>
-      </c>
+      <c r="D2483" t="inlineStr"/>
       <c r="E2483" t="inlineStr"/>
-      <c r="F2483" t="inlineStr">
-        <is>
-          <t>-8.1%</t>
-        </is>
-      </c>
+      <c r="F2483" t="inlineStr"/>
       <c r="G2483" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2484">
       <c r="A2484" t="inlineStr">
         <is>
-          <t>2025-05-27 18:00:00+05:30</t>
+          <t>2025-05-30 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B2484" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirAPR</t>
+          <t>Wholesale Inventories MoM AdvAPR</t>
         </is>
       </c>
       <c r="C2484" t="inlineStr"/>
       <c r="D2484" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="E2484" t="inlineStr"/>
-      <c r="F2484" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+      <c r="F2484" t="inlineStr"/>
       <c r="G2484" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2485">
       <c r="A2485" t="inlineStr">
         <is>
-          <t>2025-05-27 18:00:00+05:30</t>
+          <t>2025-05-30 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B2485" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMAPR</t>
+          <t>PCE Price Index YoYAPR</t>
         </is>
       </c>
       <c r="C2485" t="inlineStr"/>
       <c r="D2485" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
       <c r="E2485" t="inlineStr"/>
-      <c r="F2485" t="inlineStr">
-        <is>
-          <t>-6.8%</t>
-        </is>
-      </c>
+      <c r="F2485" t="inlineStr"/>
       <c r="G2485" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2486">
       <c r="A2486" t="inlineStr">
         <is>
-          <t>2025-05-27 18:00:00+05:30</t>
+          <t>2025-05-30 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B2486" t="inlineStr">
         <is>
-          <t>Durable Goods Orders MoMAPR</t>
+          <t>Goods Trade Balance AdvAPR</t>
         </is>
       </c>
       <c r="C2486" t="inlineStr"/>
       <c r="D2486" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>$-161.99B</t>
         </is>
       </c>
       <c r="E2486" t="inlineStr"/>
       <c r="F2486" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>$-159.0B</t>
         </is>
       </c>
       <c r="G2486" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2487">
       <c r="A2487" t="inlineStr">
         <is>
-          <t>2025-05-27 18:00:00+05:30</t>
+          <t>2025-05-30 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B2487" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMAPR</t>
+          <t>Core PCE Price Index MoMAPR</t>
         </is>
       </c>
       <c r="C2487" t="inlineStr"/>
       <c r="D2487" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E2487" t="inlineStr"/>
-      <c r="F2487" t="inlineStr">
-        <is>
-          <t>-0.2%</t>
-        </is>
-      </c>
+      <c r="F2487" t="inlineStr"/>
       <c r="G2487" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2488">
       <c r="A2488" t="inlineStr">
         <is>
-          <t>2025-05-27 18:00:00+05:30</t>
+          <t>2025-05-30 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B2488" t="inlineStr">
         <is>
-          <t>Non Defense Goods Orders Ex AirAPR</t>
+          <t>Core PCE Price Index YoYAPR</t>
         </is>
       </c>
       <c r="C2488" t="inlineStr"/>
       <c r="D2488" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>2.6%</t>
         </is>
       </c>
       <c r="E2488" t="inlineStr"/>
-      <c r="F2488" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
+      <c r="F2488" t="inlineStr"/>
       <c r="G2488" t="n">
         <v>3</v>
       </c>
@@ -69981,112 +69913,120 @@
     <row r="2489">
       <c r="A2489" t="inlineStr">
         <is>
-          <t>2025-05-27 18:00:00+05:30</t>
+          <t>2025-05-30 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B2489" t="inlineStr">
         <is>
-          <t>Durable Goods Orders ex Defense MoMAPR</t>
+          <t>Personal Income MoMAPR</t>
         </is>
       </c>
       <c r="C2489" t="inlineStr"/>
       <c r="D2489" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="E2489" t="inlineStr"/>
       <c r="F2489" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>0.4%</t>
         </is>
       </c>
       <c r="G2489" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2490">
       <c r="A2490" t="inlineStr">
         <is>
-          <t>2025-05-27 18:00:00+05:30</t>
+          <t>2025-05-30 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B2490" t="inlineStr">
         <is>
-          <t>Durable Goods Orders Ex Transp MoMAPR</t>
+          <t>Personal Spending MoMAPR</t>
         </is>
       </c>
       <c r="C2490" t="inlineStr"/>
       <c r="D2490" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="E2490" t="inlineStr"/>
       <c r="F2490" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="G2490" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2491">
       <c r="A2491" t="inlineStr">
         <is>
-          <t>2025-05-27 18:25:00+05:30</t>
+          <t>2025-05-30 18:00:00+05:30</t>
         </is>
       </c>
       <c r="B2491" t="inlineStr">
         <is>
-          <t>Redbook YoYMAY/24</t>
+          <t>PCE Price Index MoMAPR</t>
         </is>
       </c>
       <c r="C2491" t="inlineStr"/>
-      <c r="D2491" t="inlineStr"/>
+      <c r="D2491" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
       <c r="E2491" t="inlineStr"/>
       <c r="F2491" t="inlineStr"/>
       <c r="G2491" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2492">
       <c r="A2492" t="inlineStr">
         <is>
-          <t>2025-05-27 18:25:00+05:30</t>
+          <t>2025-05-30 19:15:00+05:30</t>
         </is>
       </c>
       <c r="B2492" t="inlineStr">
         <is>
-          <t>Redbook YoYMAY/24</t>
+          <t>Chicago PMIMAY</t>
         </is>
       </c>
       <c r="C2492" t="inlineStr"/>
-      <c r="D2492" t="inlineStr"/>
+      <c r="D2492" t="inlineStr">
+        <is>
+          <t>44.6</t>
+        </is>
+      </c>
       <c r="E2492" t="inlineStr"/>
-      <c r="F2492" t="inlineStr"/>
+      <c r="F2492" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
       <c r="G2492" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2493">
       <c r="A2493" t="inlineStr">
         <is>
-          <t>2025-05-27 18:30:00+05:30</t>
+          <t>2025-05-30 19:30:00+05:30</t>
         </is>
       </c>
       <c r="B2493" t="inlineStr">
         <is>
-          <t>House Price Index YoYMAR</t>
+          <t>Michigan Consumer Expectations FinalMAY</t>
         </is>
       </c>
       <c r="C2493" t="inlineStr"/>
-      <c r="D2493" t="inlineStr">
-        <is>
-          <t>3.9%</t>
-        </is>
-      </c>
+      <c r="D2493" t="inlineStr"/>
       <c r="E2493" t="inlineStr"/>
       <c r="F2493" t="inlineStr"/>
       <c r="G2493" t="n">
@@ -70096,26 +70036,22 @@
     <row r="2494">
       <c r="A2494" t="inlineStr">
         <is>
-          <t>2025-05-27 18:30:00+05:30</t>
+          <t>2025-05-30 19:30:00+05:30</t>
         </is>
       </c>
       <c r="B2494" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMMAR</t>
+          <t>Michigan Inflation Expectations FinalMAY</t>
         </is>
       </c>
       <c r="C2494" t="inlineStr"/>
       <c r="D2494" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="E2494" t="inlineStr"/>
-      <c r="F2494" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+      <c r="F2494" t="inlineStr"/>
       <c r="G2494" t="n">
         <v>3</v>
       </c>
@@ -70123,26 +70059,18 @@
     <row r="2495">
       <c r="A2495" t="inlineStr">
         <is>
-          <t>2025-05-27 18:30:00+05:30</t>
+          <t>2025-05-30 19:30:00+05:30</t>
         </is>
       </c>
       <c r="B2495" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYMAR</t>
+          <t>Michigan Consumer Sentiment FinalMAY</t>
         </is>
       </c>
       <c r="C2495" t="inlineStr"/>
-      <c r="D2495" t="inlineStr">
-        <is>
-          <t>4.5%</t>
-        </is>
-      </c>
+      <c r="D2495" t="inlineStr"/>
       <c r="E2495" t="inlineStr"/>
-      <c r="F2495" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
+      <c r="F2495" t="inlineStr"/>
       <c r="G2495" t="n">
         <v>2</v>
       </c>
@@ -70150,20 +70078,16 @@
     <row r="2496">
       <c r="A2496" t="inlineStr">
         <is>
-          <t>2025-05-27 18:30:00+05:30</t>
+          <t>2025-05-30 19:30:00+05:30</t>
         </is>
       </c>
       <c r="B2496" t="inlineStr">
         <is>
-          <t>House Price Index MoMMAR</t>
+          <t>Michigan Current Conditions FinalMAY</t>
         </is>
       </c>
       <c r="C2496" t="inlineStr"/>
-      <c r="D2496" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
+      <c r="D2496" t="inlineStr"/>
       <c r="E2496" t="inlineStr"/>
       <c r="F2496" t="inlineStr"/>
       <c r="G2496" t="n">
@@ -70173,47 +70097,39 @@
     <row r="2497">
       <c r="A2497" t="inlineStr">
         <is>
-          <t>2025-05-27 18:30:00+05:30</t>
+          <t>2025-05-30 19:30:00+05:30</t>
         </is>
       </c>
       <c r="B2497" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price YoYMAR</t>
+          <t>Michigan 5 Year Inflation Expectations FinalMAY</t>
         </is>
       </c>
       <c r="C2497" t="inlineStr"/>
       <c r="D2497" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="E2497" t="inlineStr"/>
-      <c r="F2497" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
+      <c r="F2497" t="inlineStr"/>
       <c r="G2497" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2498">
       <c r="A2498" t="inlineStr">
         <is>
-          <t>2025-05-27 18:30:00+05:30</t>
+          <t>2025-05-30 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B2498" t="inlineStr">
         <is>
-          <t>House Price IndexMAR</t>
+          <t>Baker Hughes Total Rigs CountMAY/30</t>
         </is>
       </c>
       <c r="C2498" t="inlineStr"/>
-      <c r="D2498" t="inlineStr">
-        <is>
-          <t>437.3</t>
-        </is>
-      </c>
+      <c r="D2498" t="inlineStr"/>
       <c r="E2498" t="inlineStr"/>
       <c r="F2498" t="inlineStr"/>
       <c r="G2498" t="n">
@@ -70223,2691 +70139,19 @@
     <row r="2499">
       <c r="A2499" t="inlineStr">
         <is>
-          <t>2025-05-27 18:30:00+05:30</t>
+          <t>2025-05-30 22:30:00+05:30</t>
         </is>
       </c>
       <c r="B2499" t="inlineStr">
         <is>
-          <t>S&amp;P/Case-Shiller Home Price MoMMAR</t>
+          <t>Baker Hughes Oil Rig CountMAY/30</t>
         </is>
       </c>
       <c r="C2499" t="inlineStr"/>
-      <c r="D2499" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
+      <c r="D2499" t="inlineStr"/>
       <c r="E2499" t="inlineStr"/>
-      <c r="F2499" t="inlineStr">
-        <is>
-          <t>0.6%</t>
-        </is>
-      </c>
+      <c r="F2499" t="inlineStr"/>
       <c r="G2499" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2500">
-      <c r="A2500" t="inlineStr">
-        <is>
-          <t>2025-05-27 18:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2500" t="inlineStr">
-        <is>
-          <t>House Price Index YoYMAR</t>
-        </is>
-      </c>
-      <c r="C2500" t="inlineStr"/>
-      <c r="D2500" t="inlineStr">
-        <is>
-          <t>3.9%</t>
-        </is>
-      </c>
-      <c r="E2500" t="inlineStr"/>
-      <c r="F2500" t="inlineStr"/>
-      <c r="G2500" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2501">
-      <c r="A2501" t="inlineStr">
-        <is>
-          <t>2025-05-27 18:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2501" t="inlineStr">
-        <is>
-          <t>House Price IndexMAR</t>
-        </is>
-      </c>
-      <c r="C2501" t="inlineStr"/>
-      <c r="D2501" t="inlineStr">
-        <is>
-          <t>437.3</t>
-        </is>
-      </c>
-      <c r="E2501" t="inlineStr"/>
-      <c r="F2501" t="inlineStr"/>
-      <c r="G2501" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2502">
-      <c r="A2502" t="inlineStr">
-        <is>
-          <t>2025-05-27 18:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2502" t="inlineStr">
-        <is>
-          <t>House Price Index MoMMAR</t>
-        </is>
-      </c>
-      <c r="C2502" t="inlineStr"/>
-      <c r="D2502" t="inlineStr">
-        <is>
-          <t>0.1%</t>
-        </is>
-      </c>
-      <c r="E2502" t="inlineStr"/>
-      <c r="F2502" t="inlineStr"/>
-      <c r="G2502" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2503">
-      <c r="A2503" t="inlineStr">
-        <is>
-          <t>2025-05-27 19:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2503" t="inlineStr">
-        <is>
-          <t>CB Consumer ConfidenceMAY</t>
-        </is>
-      </c>
-      <c r="C2503" t="inlineStr"/>
-      <c r="D2503" t="inlineStr">
-        <is>
-          <t>86.0</t>
-        </is>
-      </c>
-      <c r="E2503" t="inlineStr"/>
-      <c r="F2503" t="inlineStr">
-        <is>
-          <t>86.0</t>
-        </is>
-      </c>
-      <c r="G2503" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2504">
-      <c r="A2504" t="inlineStr">
-        <is>
-          <t>2025-05-27 19:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2504" t="inlineStr">
-        <is>
-          <t>CB Consumer ConfidenceMAY</t>
-        </is>
-      </c>
-      <c r="C2504" t="inlineStr"/>
-      <c r="D2504" t="inlineStr">
-        <is>
-          <t>86.0</t>
-        </is>
-      </c>
-      <c r="E2504" t="inlineStr"/>
-      <c r="F2504" t="inlineStr">
-        <is>
-          <t>86.0</t>
-        </is>
-      </c>
-      <c r="G2504" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2505">
-      <c r="A2505" t="inlineStr">
-        <is>
-          <t>2025-05-27 20:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2505" t="inlineStr">
-        <is>
-          <t>Dallas Fed Manufacturing IndexMAY</t>
-        </is>
-      </c>
-      <c r="C2505" t="inlineStr"/>
-      <c r="D2505" t="inlineStr">
-        <is>
-          <t>-35.8</t>
-        </is>
-      </c>
-      <c r="E2505" t="inlineStr"/>
-      <c r="F2505" t="inlineStr">
-        <is>
-          <t>-25</t>
-        </is>
-      </c>
-      <c r="G2505" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2506">
-      <c r="A2506" t="inlineStr">
-        <is>
-          <t>2025-05-27 20:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2506" t="inlineStr">
-        <is>
-          <t>Dallas Fed Manufacturing IndexMAY</t>
-        </is>
-      </c>
-      <c r="C2506" t="inlineStr"/>
-      <c r="D2506" t="inlineStr">
-        <is>
-          <t>-35.8</t>
-        </is>
-      </c>
-      <c r="E2506" t="inlineStr"/>
-      <c r="F2506" t="inlineStr">
-        <is>
-          <t>-25</t>
-        </is>
-      </c>
-      <c r="G2506" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2507">
-      <c r="A2507" t="inlineStr">
-        <is>
-          <t>2025-05-27 21:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2507" t="inlineStr">
-        <is>
-          <t>3-Month Bill Auction</t>
-        </is>
-      </c>
-      <c r="C2507" t="inlineStr"/>
-      <c r="D2507" t="inlineStr">
-        <is>
-          <t>4.285%</t>
-        </is>
-      </c>
-      <c r="E2507" t="inlineStr"/>
-      <c r="F2507" t="inlineStr"/>
-      <c r="G2507" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2508">
-      <c r="A2508" t="inlineStr">
-        <is>
-          <t>2025-05-27 21:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2508" t="inlineStr">
-        <is>
-          <t>6-Month Bill Auction</t>
-        </is>
-      </c>
-      <c r="C2508" t="inlineStr"/>
-      <c r="D2508" t="inlineStr">
-        <is>
-          <t>4.140%</t>
-        </is>
-      </c>
-      <c r="E2508" t="inlineStr"/>
-      <c r="F2508" t="inlineStr"/>
-      <c r="G2508" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2509">
-      <c r="A2509" t="inlineStr">
-        <is>
-          <t>2025-05-27 21:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2509" t="inlineStr">
-        <is>
-          <t>3-Month Bill Auction</t>
-        </is>
-      </c>
-      <c r="C2509" t="inlineStr"/>
-      <c r="D2509" t="inlineStr">
-        <is>
-          <t>4.285%</t>
-        </is>
-      </c>
-      <c r="E2509" t="inlineStr"/>
-      <c r="F2509" t="inlineStr"/>
-      <c r="G2509" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2510">
-      <c r="A2510" t="inlineStr">
-        <is>
-          <t>2025-05-27 21:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2510" t="inlineStr">
-        <is>
-          <t>6-Month Bill Auction</t>
-        </is>
-      </c>
-      <c r="C2510" t="inlineStr"/>
-      <c r="D2510" t="inlineStr">
-        <is>
-          <t>4.140%</t>
-        </is>
-      </c>
-      <c r="E2510" t="inlineStr"/>
-      <c r="F2510" t="inlineStr"/>
-      <c r="G2510" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2511">
-      <c r="A2511" t="inlineStr">
-        <is>
-          <t>2025-05-27 21:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2511" t="inlineStr">
-        <is>
-          <t>2-Year Note Auction</t>
-        </is>
-      </c>
-      <c r="C2511" t="inlineStr"/>
-      <c r="D2511" t="inlineStr"/>
-      <c r="E2511" t="inlineStr"/>
-      <c r="F2511" t="inlineStr"/>
-      <c r="G2511" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2512">
-      <c r="A2512" t="inlineStr">
-        <is>
-          <t>2025-05-27 21:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2512" t="inlineStr">
-        <is>
-          <t>2-Year Note Auction</t>
-        </is>
-      </c>
-      <c r="C2512" t="inlineStr"/>
-      <c r="D2512" t="inlineStr"/>
-      <c r="E2512" t="inlineStr"/>
-      <c r="F2512" t="inlineStr"/>
-      <c r="G2512" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2513">
-      <c r="A2513" t="inlineStr">
-        <is>
-          <t>2025-05-27 22:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2513" t="inlineStr">
-        <is>
-          <t>Money SupplyAPR</t>
-        </is>
-      </c>
-      <c r="C2513" t="inlineStr"/>
-      <c r="D2513" t="inlineStr">
-        <is>
-          <t>$21.76T</t>
-        </is>
-      </c>
-      <c r="E2513" t="inlineStr"/>
-      <c r="F2513" t="inlineStr"/>
-      <c r="G2513" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2514">
-      <c r="A2514" t="inlineStr">
-        <is>
-          <t>2025-05-27 22:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2514" t="inlineStr">
-        <is>
-          <t>Money SupplyAPR</t>
-        </is>
-      </c>
-      <c r="C2514" t="inlineStr"/>
-      <c r="D2514" t="inlineStr">
-        <is>
-          <t>$21.76T</t>
-        </is>
-      </c>
-      <c r="E2514" t="inlineStr"/>
-      <c r="F2514" t="inlineStr"/>
-      <c r="G2514" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2515">
-      <c r="A2515" t="inlineStr">
-        <is>
-          <t>2025-05-28 16:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2515" t="inlineStr">
-        <is>
-          <t>MBA Mortgage Refinance IndexMAY/23</t>
-        </is>
-      </c>
-      <c r="C2515" t="inlineStr"/>
-      <c r="D2515" t="inlineStr"/>
-      <c r="E2515" t="inlineStr"/>
-      <c r="F2515" t="inlineStr"/>
-      <c r="G2515" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2516">
-      <c r="A2516" t="inlineStr">
-        <is>
-          <t>2025-05-28 16:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2516" t="inlineStr">
-        <is>
-          <t>MBA Mortgage ApplicationsMAY/23</t>
-        </is>
-      </c>
-      <c r="C2516" t="inlineStr"/>
-      <c r="D2516" t="inlineStr"/>
-      <c r="E2516" t="inlineStr"/>
-      <c r="F2516" t="inlineStr"/>
-      <c r="G2516" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2517">
-      <c r="A2517" t="inlineStr">
-        <is>
-          <t>2025-05-28 16:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2517" t="inlineStr">
-        <is>
-          <t>MBA Mortgage Market IndexMAY/23</t>
-        </is>
-      </c>
-      <c r="C2517" t="inlineStr"/>
-      <c r="D2517" t="inlineStr"/>
-      <c r="E2517" t="inlineStr"/>
-      <c r="F2517" t="inlineStr"/>
-      <c r="G2517" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2518">
-      <c r="A2518" t="inlineStr">
-        <is>
-          <t>2025-05-28 16:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2518" t="inlineStr">
-        <is>
-          <t>MBA Purchase IndexMAY/23</t>
-        </is>
-      </c>
-      <c r="C2518" t="inlineStr"/>
-      <c r="D2518" t="inlineStr"/>
-      <c r="E2518" t="inlineStr"/>
-      <c r="F2518" t="inlineStr"/>
-      <c r="G2518" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2519">
-      <c r="A2519" t="inlineStr">
-        <is>
-          <t>2025-05-28 16:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2519" t="inlineStr">
-        <is>
-          <t>MBA 30-Year Mortgage RateMAY/23</t>
-        </is>
-      </c>
-      <c r="C2519" t="inlineStr"/>
-      <c r="D2519" t="inlineStr"/>
-      <c r="E2519" t="inlineStr"/>
-      <c r="F2519" t="inlineStr"/>
-      <c r="G2519" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2520">
-      <c r="A2520" t="inlineStr">
-        <is>
-          <t>2025-05-28 16:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2520" t="inlineStr">
-        <is>
-          <t>MBA Mortgage Refinance IndexMAY/23</t>
-        </is>
-      </c>
-      <c r="C2520" t="inlineStr"/>
-      <c r="D2520" t="inlineStr"/>
-      <c r="E2520" t="inlineStr"/>
-      <c r="F2520" t="inlineStr"/>
-      <c r="G2520" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2521">
-      <c r="A2521" t="inlineStr">
-        <is>
-          <t>2025-05-28 16:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2521" t="inlineStr">
-        <is>
-          <t>MBA 30-Year Mortgage RateMAY/23</t>
-        </is>
-      </c>
-      <c r="C2521" t="inlineStr"/>
-      <c r="D2521" t="inlineStr"/>
-      <c r="E2521" t="inlineStr"/>
-      <c r="F2521" t="inlineStr"/>
-      <c r="G2521" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2522">
-      <c r="A2522" t="inlineStr">
-        <is>
-          <t>2025-05-28 16:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2522" t="inlineStr">
-        <is>
-          <t>MBA Mortgage ApplicationsMAY/23</t>
-        </is>
-      </c>
-      <c r="C2522" t="inlineStr"/>
-      <c r="D2522" t="inlineStr"/>
-      <c r="E2522" t="inlineStr"/>
-      <c r="F2522" t="inlineStr"/>
-      <c r="G2522" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2523">
-      <c r="A2523" t="inlineStr">
-        <is>
-          <t>2025-05-28 16:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2523" t="inlineStr">
-        <is>
-          <t>MBA Mortgage Market IndexMAY/23</t>
-        </is>
-      </c>
-      <c r="C2523" t="inlineStr"/>
-      <c r="D2523" t="inlineStr"/>
-      <c r="E2523" t="inlineStr"/>
-      <c r="F2523" t="inlineStr"/>
-      <c r="G2523" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2524">
-      <c r="A2524" t="inlineStr">
-        <is>
-          <t>2025-05-28 16:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2524" t="inlineStr">
-        <is>
-          <t>MBA Purchase IndexMAY/23</t>
-        </is>
-      </c>
-      <c r="C2524" t="inlineStr"/>
-      <c r="D2524" t="inlineStr"/>
-      <c r="E2524" t="inlineStr"/>
-      <c r="F2524" t="inlineStr"/>
-      <c r="G2524" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2525">
-      <c r="A2525" t="inlineStr">
-        <is>
-          <t>2025-05-28 19:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2525" t="inlineStr">
-        <is>
-          <t>Richmond Fed Manufacturing Shipments IndexMAY</t>
-        </is>
-      </c>
-      <c r="C2525" t="inlineStr"/>
-      <c r="D2525" t="inlineStr">
-        <is>
-          <t>-17</t>
-        </is>
-      </c>
-      <c r="E2525" t="inlineStr"/>
-      <c r="F2525" t="inlineStr">
-        <is>
-          <t>-11</t>
-        </is>
-      </c>
-      <c r="G2525" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2526">
-      <c r="A2526" t="inlineStr">
-        <is>
-          <t>2025-05-28 19:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2526" t="inlineStr">
-        <is>
-          <t>Richmond Fed Services Revenues IndexMAY</t>
-        </is>
-      </c>
-      <c r="C2526" t="inlineStr"/>
-      <c r="D2526" t="inlineStr">
-        <is>
-          <t>-7</t>
-        </is>
-      </c>
-      <c r="E2526" t="inlineStr"/>
-      <c r="F2526" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="G2526" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2527">
-      <c r="A2527" t="inlineStr">
-        <is>
-          <t>2025-05-28 19:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2527" t="inlineStr">
-        <is>
-          <t>Richmond Fed Services Revenues IndexMAY</t>
-        </is>
-      </c>
-      <c r="C2527" t="inlineStr"/>
-      <c r="D2527" t="inlineStr">
-        <is>
-          <t>-7</t>
-        </is>
-      </c>
-      <c r="E2527" t="inlineStr"/>
-      <c r="F2527" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="G2527" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2528">
-      <c r="A2528" t="inlineStr">
-        <is>
-          <t>2025-05-28 19:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2528" t="inlineStr">
-        <is>
-          <t>Richmond Fed Manufacturing Shipments IndexMAY</t>
-        </is>
-      </c>
-      <c r="C2528" t="inlineStr"/>
-      <c r="D2528" t="inlineStr">
-        <is>
-          <t>-17</t>
-        </is>
-      </c>
-      <c r="E2528" t="inlineStr"/>
-      <c r="F2528" t="inlineStr">
-        <is>
-          <t>-11</t>
-        </is>
-      </c>
-      <c r="G2528" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2529">
-      <c r="A2529" t="inlineStr">
-        <is>
-          <t>2025-05-28 19:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2529" t="inlineStr">
-        <is>
-          <t>Richmond Fed Manufacturing IndexMAY</t>
-        </is>
-      </c>
-      <c r="C2529" t="inlineStr"/>
-      <c r="D2529" t="inlineStr">
-        <is>
-          <t>-13</t>
-        </is>
-      </c>
-      <c r="E2529" t="inlineStr"/>
-      <c r="F2529" t="inlineStr">
-        <is>
-          <t>-11</t>
-        </is>
-      </c>
-      <c r="G2529" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2530">
-      <c r="A2530" t="inlineStr">
-        <is>
-          <t>2025-05-28 19:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2530" t="inlineStr">
-        <is>
-          <t>Richmond Fed Manufacturing IndexMAY</t>
-        </is>
-      </c>
-      <c r="C2530" t="inlineStr"/>
-      <c r="D2530" t="inlineStr">
-        <is>
-          <t>-13</t>
-        </is>
-      </c>
-      <c r="E2530" t="inlineStr"/>
-      <c r="F2530" t="inlineStr">
-        <is>
-          <t>-11</t>
-        </is>
-      </c>
-      <c r="G2530" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2531">
-      <c r="A2531" t="inlineStr">
-        <is>
-          <t>2025-05-28 20:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2531" t="inlineStr">
-        <is>
-          <t>Dallas Fed Services IndexMAY</t>
-        </is>
-      </c>
-      <c r="C2531" t="inlineStr"/>
-      <c r="D2531" t="inlineStr">
-        <is>
-          <t>-19.4</t>
-        </is>
-      </c>
-      <c r="E2531" t="inlineStr"/>
-      <c r="F2531" t="inlineStr">
-        <is>
-          <t>-10</t>
-        </is>
-      </c>
-      <c r="G2531" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2532">
-      <c r="A2532" t="inlineStr">
-        <is>
-          <t>2025-05-28 20:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2532" t="inlineStr">
-        <is>
-          <t>Dallas Fed Services Revenues IndexMAY</t>
-        </is>
-      </c>
-      <c r="C2532" t="inlineStr"/>
-      <c r="D2532" t="inlineStr">
-        <is>
-          <t>3.8</t>
-        </is>
-      </c>
-      <c r="E2532" t="inlineStr"/>
-      <c r="F2532" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G2532" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2533">
-      <c r="A2533" t="inlineStr">
-        <is>
-          <t>2025-05-28 20:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2533" t="inlineStr">
-        <is>
-          <t>Dallas Fed Services IndexMAY</t>
-        </is>
-      </c>
-      <c r="C2533" t="inlineStr"/>
-      <c r="D2533" t="inlineStr">
-        <is>
-          <t>-19.4</t>
-        </is>
-      </c>
-      <c r="E2533" t="inlineStr"/>
-      <c r="F2533" t="inlineStr">
-        <is>
-          <t>-10</t>
-        </is>
-      </c>
-      <c r="G2533" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2534">
-      <c r="A2534" t="inlineStr">
-        <is>
-          <t>2025-05-28 20:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2534" t="inlineStr">
-        <is>
-          <t>Dallas Fed Services Revenues IndexMAY</t>
-        </is>
-      </c>
-      <c r="C2534" t="inlineStr"/>
-      <c r="D2534" t="inlineStr">
-        <is>
-          <t>3.8</t>
-        </is>
-      </c>
-      <c r="E2534" t="inlineStr"/>
-      <c r="F2534" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G2534" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2535">
-      <c r="A2535" t="inlineStr">
-        <is>
-          <t>2025-05-28 21:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2535" t="inlineStr">
-        <is>
-          <t>17-Week Bill Auction</t>
-        </is>
-      </c>
-      <c r="C2535" t="inlineStr"/>
-      <c r="D2535" t="inlineStr"/>
-      <c r="E2535" t="inlineStr"/>
-      <c r="F2535" t="inlineStr"/>
-      <c r="G2535" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2536">
-      <c r="A2536" t="inlineStr">
-        <is>
-          <t>2025-05-28 21:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2536" t="inlineStr">
-        <is>
-          <t>17-Week Bill Auction</t>
-        </is>
-      </c>
-      <c r="C2536" t="inlineStr"/>
-      <c r="D2536" t="inlineStr"/>
-      <c r="E2536" t="inlineStr"/>
-      <c r="F2536" t="inlineStr"/>
-      <c r="G2536" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2537">
-      <c r="A2537" t="inlineStr">
-        <is>
-          <t>2025-05-28 21:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2537" t="inlineStr">
-        <is>
-          <t>5-Year Note Auction</t>
-        </is>
-      </c>
-      <c r="C2537" t="inlineStr"/>
-      <c r="D2537" t="inlineStr">
-        <is>
-          <t>3.995%</t>
-        </is>
-      </c>
-      <c r="E2537" t="inlineStr"/>
-      <c r="F2537" t="inlineStr"/>
-      <c r="G2537" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2538">
-      <c r="A2538" t="inlineStr">
-        <is>
-          <t>2025-05-28 21:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2538" t="inlineStr">
-        <is>
-          <t>5-Year Note Auction</t>
-        </is>
-      </c>
-      <c r="C2538" t="inlineStr"/>
-      <c r="D2538" t="inlineStr">
-        <is>
-          <t>3.995%</t>
-        </is>
-      </c>
-      <c r="E2538" t="inlineStr"/>
-      <c r="F2538" t="inlineStr"/>
-      <c r="G2538" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2539">
-      <c r="A2539" t="inlineStr">
-        <is>
-          <t>2025-05-28 22:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2539" t="inlineStr">
-        <is>
-          <t>2-Year FRN Auction</t>
-        </is>
-      </c>
-      <c r="C2539" t="inlineStr"/>
-      <c r="D2539" t="inlineStr">
-        <is>
-          <t>0.160%</t>
-        </is>
-      </c>
-      <c r="E2539" t="inlineStr"/>
-      <c r="F2539" t="inlineStr"/>
-      <c r="G2539" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2540">
-      <c r="A2540" t="inlineStr">
-        <is>
-          <t>2025-05-28 22:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2540" t="inlineStr">
-        <is>
-          <t>2-Year FRN Auction</t>
-        </is>
-      </c>
-      <c r="C2540" t="inlineStr"/>
-      <c r="D2540" t="inlineStr">
-        <is>
-          <t>0.160%</t>
-        </is>
-      </c>
-      <c r="E2540" t="inlineStr"/>
-      <c r="F2540" t="inlineStr"/>
-      <c r="G2540" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2541">
-      <c r="A2541" t="inlineStr">
-        <is>
-          <t>2025-05-28 23:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2541" t="inlineStr">
-        <is>
-          <t>FOMC Minutes</t>
-        </is>
-      </c>
-      <c r="C2541" t="inlineStr"/>
-      <c r="D2541" t="inlineStr"/>
-      <c r="E2541" t="inlineStr"/>
-      <c r="F2541" t="inlineStr"/>
-      <c r="G2541" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2542">
-      <c r="A2542" t="inlineStr">
-        <is>
-          <t>2025-05-28 23:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2542" t="inlineStr">
-        <is>
-          <t>FOMC Minutes</t>
-        </is>
-      </c>
-      <c r="C2542" t="inlineStr"/>
-      <c r="D2542" t="inlineStr"/>
-      <c r="E2542" t="inlineStr"/>
-      <c r="F2542" t="inlineStr"/>
-      <c r="G2542" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2543">
-      <c r="A2543" t="inlineStr">
-        <is>
-          <t>2025-05-29 02:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2543" t="inlineStr">
-        <is>
-          <t>API Crude Oil Stock ChangeMAY/23</t>
-        </is>
-      </c>
-      <c r="C2543" t="inlineStr"/>
-      <c r="D2543" t="inlineStr"/>
-      <c r="E2543" t="inlineStr"/>
-      <c r="F2543" t="inlineStr"/>
-      <c r="G2543" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2544">
-      <c r="A2544" t="inlineStr">
-        <is>
-          <t>2025-05-29 02:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2544" t="inlineStr">
-        <is>
-          <t>API Crude Oil Stock ChangeMAY/23</t>
-        </is>
-      </c>
-      <c r="C2544" t="inlineStr"/>
-      <c r="D2544" t="inlineStr"/>
-      <c r="E2544" t="inlineStr"/>
-      <c r="F2544" t="inlineStr"/>
-      <c r="G2544" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2545">
-      <c r="A2545" t="inlineStr">
-        <is>
-          <t>2025-05-29 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2545" t="inlineStr">
-        <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ1</t>
-        </is>
-      </c>
-      <c r="C2545" t="inlineStr"/>
-      <c r="D2545" t="inlineStr">
-        <is>
-          <t>2.4%</t>
-        </is>
-      </c>
-      <c r="E2545" t="inlineStr"/>
-      <c r="F2545" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
-      <c r="G2545" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2546">
-      <c r="A2546" t="inlineStr">
-        <is>
-          <t>2025-05-29 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2546" t="inlineStr">
-        <is>
-          <t>GDP Sales QoQ 2nd EstQ1</t>
-        </is>
-      </c>
-      <c r="C2546" t="inlineStr"/>
-      <c r="D2546" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="E2546" t="inlineStr">
-        <is>
-          <t>-2.5%</t>
-        </is>
-      </c>
-      <c r="F2546" t="inlineStr">
-        <is>
-          <t>-2.5%</t>
-        </is>
-      </c>
-      <c r="G2546" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2547">
-      <c r="A2547" t="inlineStr">
-        <is>
-          <t>2025-05-29 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2547" t="inlineStr">
-        <is>
-          <t>PCE Prices QoQ 2nd EstQ1</t>
-        </is>
-      </c>
-      <c r="C2547" t="inlineStr"/>
-      <c r="D2547" t="inlineStr">
-        <is>
-          <t>2.4%</t>
-        </is>
-      </c>
-      <c r="E2547" t="inlineStr">
-        <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="F2547" t="inlineStr">
-        <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="G2547" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2548">
-      <c r="A2548" t="inlineStr">
-        <is>
-          <t>2025-05-29 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2548" t="inlineStr">
-        <is>
-          <t>GDP Growth Rate QoQ 2nd EstQ1</t>
-        </is>
-      </c>
-      <c r="C2548" t="inlineStr"/>
-      <c r="D2548" t="inlineStr">
-        <is>
-          <t>2.4%</t>
-        </is>
-      </c>
-      <c r="E2548" t="inlineStr"/>
-      <c r="F2548" t="inlineStr">
-        <is>
-          <t>-0.3%</t>
-        </is>
-      </c>
-      <c r="G2548" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2549">
-      <c r="A2549" t="inlineStr">
-        <is>
-          <t>2025-05-29 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2549" t="inlineStr">
-        <is>
-          <t>Corporate Profits QoQ PrelQ1</t>
-        </is>
-      </c>
-      <c r="C2549" t="inlineStr"/>
-      <c r="D2549" t="inlineStr">
-        <is>
-          <t>5.9%</t>
-        </is>
-      </c>
-      <c r="E2549" t="inlineStr"/>
-      <c r="F2549" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="G2549" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2550">
-      <c r="A2550" t="inlineStr">
-        <is>
-          <t>2025-05-29 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2550" t="inlineStr">
-        <is>
-          <t>GDP Price Index QoQ 2nd EstQ1</t>
-        </is>
-      </c>
-      <c r="C2550" t="inlineStr"/>
-      <c r="D2550" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="E2550" t="inlineStr"/>
-      <c r="F2550" t="inlineStr">
-        <is>
-          <t>3.7%</t>
-        </is>
-      </c>
-      <c r="G2550" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2551">
-      <c r="A2551" t="inlineStr">
-        <is>
-          <t>2025-05-29 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2551" t="inlineStr">
-        <is>
-          <t>Initial Jobless ClaimsMAY/24</t>
-        </is>
-      </c>
-      <c r="C2551" t="inlineStr"/>
-      <c r="D2551" t="inlineStr"/>
-      <c r="E2551" t="inlineStr"/>
-      <c r="F2551" t="inlineStr"/>
-      <c r="G2551" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2552">
-      <c r="A2552" t="inlineStr">
-        <is>
-          <t>2025-05-29 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2552" t="inlineStr">
-        <is>
-          <t>Continuing Jobless ClaimsMAY/17</t>
-        </is>
-      </c>
-      <c r="C2552" t="inlineStr"/>
-      <c r="D2552" t="inlineStr"/>
-      <c r="E2552" t="inlineStr"/>
-      <c r="F2552" t="inlineStr"/>
-      <c r="G2552" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2553">
-      <c r="A2553" t="inlineStr">
-        <is>
-          <t>2025-05-29 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2553" t="inlineStr">
-        <is>
-          <t>Core PCE Prices QoQ 2nd EstQ1</t>
-        </is>
-      </c>
-      <c r="C2553" t="inlineStr"/>
-      <c r="D2553" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="E2553" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="F2553" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="G2553" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2554">
-      <c r="A2554" t="inlineStr">
-        <is>
-          <t>2025-05-29 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2554" t="inlineStr">
-        <is>
-          <t>GDP Sales QoQ 2nd EstQ1</t>
-        </is>
-      </c>
-      <c r="C2554" t="inlineStr"/>
-      <c r="D2554" t="inlineStr">
-        <is>
-          <t>3.3%</t>
-        </is>
-      </c>
-      <c r="E2554" t="inlineStr">
-        <is>
-          <t>-2.5%</t>
-        </is>
-      </c>
-      <c r="F2554" t="inlineStr">
-        <is>
-          <t>-2.5%</t>
-        </is>
-      </c>
-      <c r="G2554" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2555">
-      <c r="A2555" t="inlineStr">
-        <is>
-          <t>2025-05-29 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2555" t="inlineStr">
-        <is>
-          <t>Jobless Claims 4-week AverageMAY/24</t>
-        </is>
-      </c>
-      <c r="C2555" t="inlineStr"/>
-      <c r="D2555" t="inlineStr"/>
-      <c r="E2555" t="inlineStr"/>
-      <c r="F2555" t="inlineStr"/>
-      <c r="G2555" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2556">
-      <c r="A2556" t="inlineStr">
-        <is>
-          <t>2025-05-29 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2556" t="inlineStr">
-        <is>
-          <t>Initial Jobless ClaimsMAY/24</t>
-        </is>
-      </c>
-      <c r="C2556" t="inlineStr"/>
-      <c r="D2556" t="inlineStr"/>
-      <c r="E2556" t="inlineStr"/>
-      <c r="F2556" t="inlineStr"/>
-      <c r="G2556" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2557">
-      <c r="A2557" t="inlineStr">
-        <is>
-          <t>2025-05-29 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2557" t="inlineStr">
-        <is>
-          <t>PCE Prices QoQ 2nd EstQ1</t>
-        </is>
-      </c>
-      <c r="C2557" t="inlineStr"/>
-      <c r="D2557" t="inlineStr">
-        <is>
-          <t>2.4%</t>
-        </is>
-      </c>
-      <c r="E2557" t="inlineStr">
-        <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="F2557" t="inlineStr">
-        <is>
-          <t>3.6%</t>
-        </is>
-      </c>
-      <c r="G2557" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2558">
-      <c r="A2558" t="inlineStr">
-        <is>
-          <t>2025-05-29 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2558" t="inlineStr">
-        <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ1</t>
-        </is>
-      </c>
-      <c r="C2558" t="inlineStr"/>
-      <c r="D2558" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="E2558" t="inlineStr">
-        <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="F2558" t="inlineStr">
-        <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="G2558" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2559">
-      <c r="A2559" t="inlineStr">
-        <is>
-          <t>2025-05-29 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2559" t="inlineStr">
-        <is>
-          <t>Corporate Profits QoQ PrelQ1</t>
-        </is>
-      </c>
-      <c r="C2559" t="inlineStr"/>
-      <c r="D2559" t="inlineStr">
-        <is>
-          <t>5.9%</t>
-        </is>
-      </c>
-      <c r="E2559" t="inlineStr"/>
-      <c r="F2559" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="G2559" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2560">
-      <c r="A2560" t="inlineStr">
-        <is>
-          <t>2025-05-29 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2560" t="inlineStr">
-        <is>
-          <t>Jobless Claims 4-week AverageMAY/24</t>
-        </is>
-      </c>
-      <c r="C2560" t="inlineStr"/>
-      <c r="D2560" t="inlineStr"/>
-      <c r="E2560" t="inlineStr"/>
-      <c r="F2560" t="inlineStr"/>
-      <c r="G2560" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2561">
-      <c r="A2561" t="inlineStr">
-        <is>
-          <t>2025-05-29 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2561" t="inlineStr">
-        <is>
-          <t>Core PCE Prices QoQ 2nd EstQ1</t>
-        </is>
-      </c>
-      <c r="C2561" t="inlineStr"/>
-      <c r="D2561" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="E2561" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="F2561" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="G2561" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2562">
-      <c r="A2562" t="inlineStr">
-        <is>
-          <t>2025-05-29 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2562" t="inlineStr">
-        <is>
-          <t>Continuing Jobless ClaimsMAY/17</t>
-        </is>
-      </c>
-      <c r="C2562" t="inlineStr"/>
-      <c r="D2562" t="inlineStr"/>
-      <c r="E2562" t="inlineStr"/>
-      <c r="F2562" t="inlineStr"/>
-      <c r="G2562" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2563">
-      <c r="A2563" t="inlineStr">
-        <is>
-          <t>2025-05-29 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2563" t="inlineStr">
-        <is>
-          <t>GDP Price Index QoQ 2nd EstQ1</t>
-        </is>
-      </c>
-      <c r="C2563" t="inlineStr"/>
-      <c r="D2563" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="E2563" t="inlineStr"/>
-      <c r="F2563" t="inlineStr">
-        <is>
-          <t>3.7%</t>
-        </is>
-      </c>
-      <c r="G2563" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2564">
-      <c r="A2564" t="inlineStr">
-        <is>
-          <t>2025-05-29 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2564" t="inlineStr">
-        <is>
-          <t>Real Consumer Spending QoQ 2nd EstQ1</t>
-        </is>
-      </c>
-      <c r="C2564" t="inlineStr"/>
-      <c r="D2564" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
-      <c r="E2564" t="inlineStr">
-        <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="F2564" t="inlineStr">
-        <is>
-          <t>1.8%</t>
-        </is>
-      </c>
-      <c r="G2564" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2565">
-      <c r="A2565" t="inlineStr">
-        <is>
-          <t>2025-05-29 19:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2565" t="inlineStr">
-        <is>
-          <t>Pending Home Sales MoMAPR</t>
-        </is>
-      </c>
-      <c r="C2565" t="inlineStr"/>
-      <c r="D2565" t="inlineStr">
-        <is>
-          <t>6.1%</t>
-        </is>
-      </c>
-      <c r="E2565" t="inlineStr"/>
-      <c r="F2565" t="inlineStr">
-        <is>
-          <t>3.0%</t>
-        </is>
-      </c>
-      <c r="G2565" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2566">
-      <c r="A2566" t="inlineStr">
-        <is>
-          <t>2025-05-29 19:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2566" t="inlineStr">
-        <is>
-          <t>Pending Home Sales YoYAPR</t>
-        </is>
-      </c>
-      <c r="C2566" t="inlineStr"/>
-      <c r="D2566" t="inlineStr"/>
-      <c r="E2566" t="inlineStr"/>
-      <c r="F2566" t="inlineStr"/>
-      <c r="G2566" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2567">
-      <c r="A2567" t="inlineStr">
-        <is>
-          <t>2025-05-29 19:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2567" t="inlineStr">
-        <is>
-          <t>Pending Home Sales YoYAPR</t>
-        </is>
-      </c>
-      <c r="C2567" t="inlineStr"/>
-      <c r="D2567" t="inlineStr"/>
-      <c r="E2567" t="inlineStr"/>
-      <c r="F2567" t="inlineStr"/>
-      <c r="G2567" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2568">
-      <c r="A2568" t="inlineStr">
-        <is>
-          <t>2025-05-29 19:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2568" t="inlineStr">
-        <is>
-          <t>Pending Home Sales MoMAPR</t>
-        </is>
-      </c>
-      <c r="C2568" t="inlineStr"/>
-      <c r="D2568" t="inlineStr">
-        <is>
-          <t>6.1%</t>
-        </is>
-      </c>
-      <c r="E2568" t="inlineStr"/>
-      <c r="F2568" t="inlineStr">
-        <is>
-          <t>3.0%</t>
-        </is>
-      </c>
-      <c r="G2568" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2569">
-      <c r="A2569" t="inlineStr">
-        <is>
-          <t>2025-05-29 20:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2569" t="inlineStr">
-        <is>
-          <t>EIA Natural Gas Stocks ChangeMAY/23</t>
-        </is>
-      </c>
-      <c r="C2569" t="inlineStr"/>
-      <c r="D2569" t="inlineStr"/>
-      <c r="E2569" t="inlineStr"/>
-      <c r="F2569" t="inlineStr"/>
-      <c r="G2569" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2570">
-      <c r="A2570" t="inlineStr">
-        <is>
-          <t>2025-05-29 20:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2570" t="inlineStr">
-        <is>
-          <t>EIA Natural Gas Stocks ChangeMAY/23</t>
-        </is>
-      </c>
-      <c r="C2570" t="inlineStr"/>
-      <c r="D2570" t="inlineStr"/>
-      <c r="E2570" t="inlineStr"/>
-      <c r="F2570" t="inlineStr"/>
-      <c r="G2570" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2571">
-      <c r="A2571" t="inlineStr">
-        <is>
-          <t>2025-05-29 20:10:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2571" t="inlineStr">
-        <is>
-          <t>Fed Goolsbee Speech</t>
-        </is>
-      </c>
-      <c r="C2571" t="inlineStr"/>
-      <c r="D2571" t="inlineStr"/>
-      <c r="E2571" t="inlineStr"/>
-      <c r="F2571" t="inlineStr"/>
-      <c r="G2571" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2572">
-      <c r="A2572" t="inlineStr">
-        <is>
-          <t>2025-05-29 20:10:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2572" t="inlineStr">
-        <is>
-          <t>Fed Goolsbee Speech</t>
-        </is>
-      </c>
-      <c r="C2572" t="inlineStr"/>
-      <c r="D2572" t="inlineStr"/>
-      <c r="E2572" t="inlineStr"/>
-      <c r="F2572" t="inlineStr"/>
-      <c r="G2572" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2573">
-      <c r="A2573" t="inlineStr">
-        <is>
-          <t>2025-05-29 20:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2573" t="inlineStr">
-        <is>
-          <t>EIA Crude Oil Imports ChangeMAY/23</t>
-        </is>
-      </c>
-      <c r="C2573" t="inlineStr"/>
-      <c r="D2573" t="inlineStr"/>
-      <c r="E2573" t="inlineStr"/>
-      <c r="F2573" t="inlineStr"/>
-      <c r="G2573" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2574">
-      <c r="A2574" t="inlineStr">
-        <is>
-          <t>2025-05-29 20:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2574" t="inlineStr">
-        <is>
-          <t>EIA Gasoline Production ChangeMAY/23</t>
-        </is>
-      </c>
-      <c r="C2574" t="inlineStr"/>
-      <c r="D2574" t="inlineStr"/>
-      <c r="E2574" t="inlineStr"/>
-      <c r="F2574" t="inlineStr"/>
-      <c r="G2574" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2575">
-      <c r="A2575" t="inlineStr">
-        <is>
-          <t>2025-05-29 20:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2575" t="inlineStr">
-        <is>
-          <t>EIA Crude Oil Imports ChangeMAY/23</t>
-        </is>
-      </c>
-      <c r="C2575" t="inlineStr"/>
-      <c r="D2575" t="inlineStr"/>
-      <c r="E2575" t="inlineStr"/>
-      <c r="F2575" t="inlineStr"/>
-      <c r="G2575" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2576">
-      <c r="A2576" t="inlineStr">
-        <is>
-          <t>2025-05-29 20:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2576" t="inlineStr">
-        <is>
-          <t>EIA Distillate Stocks ChangeMAY/23</t>
-        </is>
-      </c>
-      <c r="C2576" t="inlineStr"/>
-      <c r="D2576" t="inlineStr"/>
-      <c r="E2576" t="inlineStr"/>
-      <c r="F2576" t="inlineStr"/>
-      <c r="G2576" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2577">
-      <c r="A2577" t="inlineStr">
-        <is>
-          <t>2025-05-29 20:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2577" t="inlineStr">
-        <is>
-          <t>EIA Gasoline Production ChangeMAY/23</t>
-        </is>
-      </c>
-      <c r="C2577" t="inlineStr"/>
-      <c r="D2577" t="inlineStr"/>
-      <c r="E2577" t="inlineStr"/>
-      <c r="F2577" t="inlineStr"/>
-      <c r="G2577" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2578">
-      <c r="A2578" t="inlineStr">
-        <is>
-          <t>2025-05-29 20:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2578" t="inlineStr">
-        <is>
-          <t>EIA Distillate Stocks ChangeMAY/23</t>
-        </is>
-      </c>
-      <c r="C2578" t="inlineStr"/>
-      <c r="D2578" t="inlineStr"/>
-      <c r="E2578" t="inlineStr"/>
-      <c r="F2578" t="inlineStr"/>
-      <c r="G2578" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2579">
-      <c r="A2579" t="inlineStr">
-        <is>
-          <t>2025-05-29 21:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2579" t="inlineStr">
-        <is>
-          <t>4-Week Bill Auction</t>
-        </is>
-      </c>
-      <c r="C2579" t="inlineStr"/>
-      <c r="D2579" t="inlineStr"/>
-      <c r="E2579" t="inlineStr"/>
-      <c r="F2579" t="inlineStr"/>
-      <c r="G2579" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2580">
-      <c r="A2580" t="inlineStr">
-        <is>
-          <t>2025-05-29 21:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2580" t="inlineStr">
-        <is>
-          <t>8-Week Bill Auction</t>
-        </is>
-      </c>
-      <c r="C2580" t="inlineStr"/>
-      <c r="D2580" t="inlineStr"/>
-      <c r="E2580" t="inlineStr"/>
-      <c r="F2580" t="inlineStr"/>
-      <c r="G2580" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2581">
-      <c r="A2581" t="inlineStr">
-        <is>
-          <t>2025-05-29 21:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2581" t="inlineStr">
-        <is>
-          <t>4-Week Bill Auction</t>
-        </is>
-      </c>
-      <c r="C2581" t="inlineStr"/>
-      <c r="D2581" t="inlineStr"/>
-      <c r="E2581" t="inlineStr"/>
-      <c r="F2581" t="inlineStr"/>
-      <c r="G2581" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2582">
-      <c r="A2582" t="inlineStr">
-        <is>
-          <t>2025-05-29 21:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2582" t="inlineStr">
-        <is>
-          <t>8-Week Bill Auction</t>
-        </is>
-      </c>
-      <c r="C2582" t="inlineStr"/>
-      <c r="D2582" t="inlineStr"/>
-      <c r="E2582" t="inlineStr"/>
-      <c r="F2582" t="inlineStr"/>
-      <c r="G2582" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2583">
-      <c r="A2583" t="inlineStr">
-        <is>
-          <t>2025-05-29 21:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2583" t="inlineStr">
-        <is>
-          <t>EIA Gasoline Stocks ChangeMAY/23</t>
-        </is>
-      </c>
-      <c r="C2583" t="inlineStr"/>
-      <c r="D2583" t="inlineStr"/>
-      <c r="E2583" t="inlineStr"/>
-      <c r="F2583" t="inlineStr"/>
-      <c r="G2583" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2584">
-      <c r="A2584" t="inlineStr">
-        <is>
-          <t>2025-05-29 21:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2584" t="inlineStr">
-        <is>
-          <t>EIA Gasoline Stocks ChangeMAY/23</t>
-        </is>
-      </c>
-      <c r="C2584" t="inlineStr"/>
-      <c r="D2584" t="inlineStr"/>
-      <c r="E2584" t="inlineStr"/>
-      <c r="F2584" t="inlineStr"/>
-      <c r="G2584" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2585">
-      <c r="A2585" t="inlineStr">
-        <is>
-          <t>2025-05-29 21:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2585" t="inlineStr">
-        <is>
-          <t>EIA Refinery Crude Runs ChangeMAY/23</t>
-        </is>
-      </c>
-      <c r="C2585" t="inlineStr"/>
-      <c r="D2585" t="inlineStr"/>
-      <c r="E2585" t="inlineStr"/>
-      <c r="F2585" t="inlineStr"/>
-      <c r="G2585" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2586">
-      <c r="A2586" t="inlineStr">
-        <is>
-          <t>2025-05-29 21:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2586" t="inlineStr">
-        <is>
-          <t>EIA Heating Oil Stocks ChangeMAY/23</t>
-        </is>
-      </c>
-      <c r="C2586" t="inlineStr"/>
-      <c r="D2586" t="inlineStr"/>
-      <c r="E2586" t="inlineStr"/>
-      <c r="F2586" t="inlineStr"/>
-      <c r="G2586" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2587">
-      <c r="A2587" t="inlineStr">
-        <is>
-          <t>2025-05-29 21:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2587" t="inlineStr">
-        <is>
-          <t>EIA Distillate Fuel Production ChangeMAY/23</t>
-        </is>
-      </c>
-      <c r="C2587" t="inlineStr"/>
-      <c r="D2587" t="inlineStr"/>
-      <c r="E2587" t="inlineStr"/>
-      <c r="F2587" t="inlineStr"/>
-      <c r="G2587" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2588">
-      <c r="A2588" t="inlineStr">
-        <is>
-          <t>2025-05-29 21:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2588" t="inlineStr">
-        <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeMAY/23</t>
-        </is>
-      </c>
-      <c r="C2588" t="inlineStr"/>
-      <c r="D2588" t="inlineStr"/>
-      <c r="E2588" t="inlineStr"/>
-      <c r="F2588" t="inlineStr"/>
-      <c r="G2588" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2589">
-      <c r="A2589" t="inlineStr">
-        <is>
-          <t>2025-05-29 21:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2589" t="inlineStr">
-        <is>
-          <t>7-Year Note Auction</t>
-        </is>
-      </c>
-      <c r="C2589" t="inlineStr"/>
-      <c r="D2589" t="inlineStr"/>
-      <c r="E2589" t="inlineStr"/>
-      <c r="F2589" t="inlineStr"/>
-      <c r="G2589" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2590">
-      <c r="A2590" t="inlineStr">
-        <is>
-          <t>2025-05-29 21:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2590" t="inlineStr">
-        <is>
-          <t>30-Year Mortgage RateMAY/29</t>
-        </is>
-      </c>
-      <c r="C2590" t="inlineStr"/>
-      <c r="D2590" t="inlineStr"/>
-      <c r="E2590" t="inlineStr"/>
-      <c r="F2590" t="inlineStr"/>
-      <c r="G2590" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2591">
-      <c r="A2591" t="inlineStr">
-        <is>
-          <t>2025-05-29 21:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2591" t="inlineStr">
-        <is>
-          <t>EIA Refinery Crude Runs ChangeMAY/23</t>
-        </is>
-      </c>
-      <c r="C2591" t="inlineStr"/>
-      <c r="D2591" t="inlineStr"/>
-      <c r="E2591" t="inlineStr"/>
-      <c r="F2591" t="inlineStr"/>
-      <c r="G2591" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2592">
-      <c r="A2592" t="inlineStr">
-        <is>
-          <t>2025-05-29 21:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2592" t="inlineStr">
-        <is>
-          <t>EIA Crude Oil Stocks ChangeMAY/23</t>
-        </is>
-      </c>
-      <c r="C2592" t="inlineStr"/>
-      <c r="D2592" t="inlineStr"/>
-      <c r="E2592" t="inlineStr"/>
-      <c r="F2592" t="inlineStr"/>
-      <c r="G2592" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2593">
-      <c r="A2593" t="inlineStr">
-        <is>
-          <t>2025-05-29 21:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2593" t="inlineStr">
-        <is>
-          <t>15-Year Mortgage RateMAY/29</t>
-        </is>
-      </c>
-      <c r="C2593" t="inlineStr"/>
-      <c r="D2593" t="inlineStr"/>
-      <c r="E2593" t="inlineStr"/>
-      <c r="F2593" t="inlineStr"/>
-      <c r="G2593" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2594">
-      <c r="A2594" t="inlineStr">
-        <is>
-          <t>2025-05-29 21:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2594" t="inlineStr">
-        <is>
-          <t>EIA Heating Oil Stocks ChangeMAY/23</t>
-        </is>
-      </c>
-      <c r="C2594" t="inlineStr"/>
-      <c r="D2594" t="inlineStr"/>
-      <c r="E2594" t="inlineStr"/>
-      <c r="F2594" t="inlineStr"/>
-      <c r="G2594" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2595">
-      <c r="A2595" t="inlineStr">
-        <is>
-          <t>2025-05-29 21:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2595" t="inlineStr">
-        <is>
-          <t>EIA Distillate Fuel Production ChangeMAY/23</t>
-        </is>
-      </c>
-      <c r="C2595" t="inlineStr"/>
-      <c r="D2595" t="inlineStr"/>
-      <c r="E2595" t="inlineStr"/>
-      <c r="F2595" t="inlineStr"/>
-      <c r="G2595" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2596">
-      <c r="A2596" t="inlineStr">
-        <is>
-          <t>2025-05-29 21:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2596" t="inlineStr">
-        <is>
-          <t>EIA Cushing Crude Oil Stocks ChangeMAY/23</t>
-        </is>
-      </c>
-      <c r="C2596" t="inlineStr"/>
-      <c r="D2596" t="inlineStr"/>
-      <c r="E2596" t="inlineStr"/>
-      <c r="F2596" t="inlineStr"/>
-      <c r="G2596" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2597">
-      <c r="A2597" t="inlineStr">
-        <is>
-          <t>2025-05-29 21:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2597" t="inlineStr">
-        <is>
-          <t>7-Year Note Auction</t>
-        </is>
-      </c>
-      <c r="C2597" t="inlineStr"/>
-      <c r="D2597" t="inlineStr"/>
-      <c r="E2597" t="inlineStr"/>
-      <c r="F2597" t="inlineStr"/>
-      <c r="G2597" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2598">
-      <c r="A2598" t="inlineStr">
-        <is>
-          <t>2025-05-29 21:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2598" t="inlineStr">
-        <is>
-          <t>30-Year Mortgage RateMAY/29</t>
-        </is>
-      </c>
-      <c r="C2598" t="inlineStr"/>
-      <c r="D2598" t="inlineStr"/>
-      <c r="E2598" t="inlineStr"/>
-      <c r="F2598" t="inlineStr"/>
-      <c r="G2598" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2599">
-      <c r="A2599" t="inlineStr">
-        <is>
-          <t>2025-05-29 21:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2599" t="inlineStr">
-        <is>
-          <t>EIA Crude Oil Stocks ChangeMAY/23</t>
-        </is>
-      </c>
-      <c r="C2599" t="inlineStr"/>
-      <c r="D2599" t="inlineStr"/>
-      <c r="E2599" t="inlineStr"/>
-      <c r="F2599" t="inlineStr"/>
-      <c r="G2599" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2600">
-      <c r="A2600" t="inlineStr">
-        <is>
-          <t>2025-05-29 21:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2600" t="inlineStr">
-        <is>
-          <t>15-Year Mortgage RateMAY/29</t>
-        </is>
-      </c>
-      <c r="C2600" t="inlineStr"/>
-      <c r="D2600" t="inlineStr"/>
-      <c r="E2600" t="inlineStr"/>
-      <c r="F2600" t="inlineStr"/>
-      <c r="G2600" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2601">
-      <c r="A2601" t="inlineStr">
-        <is>
-          <t>2025-05-30 02:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2601" t="inlineStr">
-        <is>
-          <t>Fed Balance SheetMAY/28</t>
-        </is>
-      </c>
-      <c r="C2601" t="inlineStr"/>
-      <c r="D2601" t="inlineStr"/>
-      <c r="E2601" t="inlineStr"/>
-      <c r="F2601" t="inlineStr"/>
-      <c r="G2601" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2602">
-      <c r="A2602" t="inlineStr">
-        <is>
-          <t>2025-05-30 02:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2602" t="inlineStr">
-        <is>
-          <t>Fed Balance SheetMAY/28</t>
-        </is>
-      </c>
-      <c r="C2602" t="inlineStr"/>
-      <c r="D2602" t="inlineStr"/>
-      <c r="E2602" t="inlineStr"/>
-      <c r="F2602" t="inlineStr"/>
-      <c r="G2602" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2603">
-      <c r="A2603" t="inlineStr">
-        <is>
-          <t>2025-05-30 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2603" t="inlineStr">
-        <is>
-          <t>Retail Inventories Ex Autos MoM AdvAPR</t>
-        </is>
-      </c>
-      <c r="C2603" t="inlineStr"/>
-      <c r="D2603" t="inlineStr"/>
-      <c r="E2603" t="inlineStr"/>
-      <c r="F2603" t="inlineStr"/>
-      <c r="G2603" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2604">
-      <c r="A2604" t="inlineStr">
-        <is>
-          <t>2025-05-30 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2604" t="inlineStr">
-        <is>
-          <t>Wholesale Inventories MoM AdvAPR</t>
-        </is>
-      </c>
-      <c r="C2604" t="inlineStr"/>
-      <c r="D2604" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="E2604" t="inlineStr"/>
-      <c r="F2604" t="inlineStr"/>
-      <c r="G2604" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2605">
-      <c r="A2605" t="inlineStr">
-        <is>
-          <t>2025-05-30 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2605" t="inlineStr">
-        <is>
-          <t>PCE Price Index YoYAPR</t>
-        </is>
-      </c>
-      <c r="C2605" t="inlineStr"/>
-      <c r="D2605" t="inlineStr">
-        <is>
-          <t>2.3%</t>
-        </is>
-      </c>
-      <c r="E2605" t="inlineStr"/>
-      <c r="F2605" t="inlineStr"/>
-      <c r="G2605" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2606">
-      <c r="A2606" t="inlineStr">
-        <is>
-          <t>2025-05-30 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2606" t="inlineStr">
-        <is>
-          <t>Goods Trade Balance AdvAPR</t>
-        </is>
-      </c>
-      <c r="C2606" t="inlineStr"/>
-      <c r="D2606" t="inlineStr">
-        <is>
-          <t>$-161.99B</t>
-        </is>
-      </c>
-      <c r="E2606" t="inlineStr"/>
-      <c r="F2606" t="inlineStr">
-        <is>
-          <t>$-159.0B</t>
-        </is>
-      </c>
-      <c r="G2606" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2607">
-      <c r="A2607" t="inlineStr">
-        <is>
-          <t>2025-05-30 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2607" t="inlineStr">
-        <is>
-          <t>Core PCE Price Index MoMAPR</t>
-        </is>
-      </c>
-      <c r="C2607" t="inlineStr"/>
-      <c r="D2607" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="E2607" t="inlineStr"/>
-      <c r="F2607" t="inlineStr"/>
-      <c r="G2607" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2608">
-      <c r="A2608" t="inlineStr">
-        <is>
-          <t>2025-05-30 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2608" t="inlineStr">
-        <is>
-          <t>Core PCE Price Index YoYAPR</t>
-        </is>
-      </c>
-      <c r="C2608" t="inlineStr"/>
-      <c r="D2608" t="inlineStr">
-        <is>
-          <t>2.6%</t>
-        </is>
-      </c>
-      <c r="E2608" t="inlineStr"/>
-      <c r="F2608" t="inlineStr"/>
-      <c r="G2608" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2609">
-      <c r="A2609" t="inlineStr">
-        <is>
-          <t>2025-05-30 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2609" t="inlineStr">
-        <is>
-          <t>Personal Income MoMAPR</t>
-        </is>
-      </c>
-      <c r="C2609" t="inlineStr"/>
-      <c r="D2609" t="inlineStr">
-        <is>
-          <t>0.5%</t>
-        </is>
-      </c>
-      <c r="E2609" t="inlineStr"/>
-      <c r="F2609" t="inlineStr">
-        <is>
-          <t>0.4%</t>
-        </is>
-      </c>
-      <c r="G2609" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2610">
-      <c r="A2610" t="inlineStr">
-        <is>
-          <t>2025-05-30 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2610" t="inlineStr">
-        <is>
-          <t>Personal Spending MoMAPR</t>
-        </is>
-      </c>
-      <c r="C2610" t="inlineStr"/>
-      <c r="D2610" t="inlineStr">
-        <is>
-          <t>0.7%</t>
-        </is>
-      </c>
-      <c r="E2610" t="inlineStr"/>
-      <c r="F2610" t="inlineStr">
-        <is>
-          <t>0.3%</t>
-        </is>
-      </c>
-      <c r="G2610" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2611">
-      <c r="A2611" t="inlineStr">
-        <is>
-          <t>2025-05-30 18:00:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2611" t="inlineStr">
-        <is>
-          <t>PCE Price Index MoMAPR</t>
-        </is>
-      </c>
-      <c r="C2611" t="inlineStr"/>
-      <c r="D2611" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="E2611" t="inlineStr"/>
-      <c r="F2611" t="inlineStr"/>
-      <c r="G2611" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2612">
-      <c r="A2612" t="inlineStr">
-        <is>
-          <t>2025-05-30 19:15:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2612" t="inlineStr">
-        <is>
-          <t>Chicago PMIMAY</t>
-        </is>
-      </c>
-      <c r="C2612" t="inlineStr"/>
-      <c r="D2612" t="inlineStr">
-        <is>
-          <t>44.6</t>
-        </is>
-      </c>
-      <c r="E2612" t="inlineStr"/>
-      <c r="F2612" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="G2612" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2613">
-      <c r="A2613" t="inlineStr">
-        <is>
-          <t>2025-05-30 19:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2613" t="inlineStr">
-        <is>
-          <t>Michigan Consumer Expectations FinalMAY</t>
-        </is>
-      </c>
-      <c r="C2613" t="inlineStr"/>
-      <c r="D2613" t="inlineStr"/>
-      <c r="E2613" t="inlineStr"/>
-      <c r="F2613" t="inlineStr"/>
-      <c r="G2613" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2614">
-      <c r="A2614" t="inlineStr">
-        <is>
-          <t>2025-05-30 19:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2614" t="inlineStr">
-        <is>
-          <t>Michigan Inflation Expectations FinalMAY</t>
-        </is>
-      </c>
-      <c r="C2614" t="inlineStr"/>
-      <c r="D2614" t="inlineStr">
-        <is>
-          <t>6.5%</t>
-        </is>
-      </c>
-      <c r="E2614" t="inlineStr"/>
-      <c r="F2614" t="inlineStr"/>
-      <c r="G2614" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2615">
-      <c r="A2615" t="inlineStr">
-        <is>
-          <t>2025-05-30 19:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2615" t="inlineStr">
-        <is>
-          <t>Michigan Consumer Sentiment FinalMAY</t>
-        </is>
-      </c>
-      <c r="C2615" t="inlineStr"/>
-      <c r="D2615" t="inlineStr"/>
-      <c r="E2615" t="inlineStr"/>
-      <c r="F2615" t="inlineStr"/>
-      <c r="G2615" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2616">
-      <c r="A2616" t="inlineStr">
-        <is>
-          <t>2025-05-30 19:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2616" t="inlineStr">
-        <is>
-          <t>Michigan Current Conditions FinalMAY</t>
-        </is>
-      </c>
-      <c r="C2616" t="inlineStr"/>
-      <c r="D2616" t="inlineStr"/>
-      <c r="E2616" t="inlineStr"/>
-      <c r="F2616" t="inlineStr"/>
-      <c r="G2616" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2617">
-      <c r="A2617" t="inlineStr">
-        <is>
-          <t>2025-05-30 19:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2617" t="inlineStr">
-        <is>
-          <t>Michigan 5 Year Inflation Expectations FinalMAY</t>
-        </is>
-      </c>
-      <c r="C2617" t="inlineStr"/>
-      <c r="D2617" t="inlineStr">
-        <is>
-          <t>4.4%</t>
-        </is>
-      </c>
-      <c r="E2617" t="inlineStr"/>
-      <c r="F2617" t="inlineStr"/>
-      <c r="G2617" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2618">
-      <c r="A2618" t="inlineStr">
-        <is>
-          <t>2025-05-30 22:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2618" t="inlineStr">
-        <is>
-          <t>Baker Hughes Total Rigs CountMAY/30</t>
-        </is>
-      </c>
-      <c r="C2618" t="inlineStr"/>
-      <c r="D2618" t="inlineStr"/>
-      <c r="E2618" t="inlineStr"/>
-      <c r="F2618" t="inlineStr"/>
-      <c r="G2618" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2619">
-      <c r="A2619" t="inlineStr">
-        <is>
-          <t>2025-05-30 22:30:00+05:30</t>
-        </is>
-      </c>
-      <c r="B2619" t="inlineStr">
-        <is>
-          <t>Baker Hughes Oil Rig CountMAY/30</t>
-        </is>
-      </c>
-      <c r="C2619" t="inlineStr"/>
-      <c r="D2619" t="inlineStr"/>
-      <c r="E2619" t="inlineStr"/>
-      <c r="F2619" t="inlineStr"/>
-      <c r="G2619" t="n">
         <v>3</v>
       </c>
     </row>
